--- a/output/yearly_population_iteration_60_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_60_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6618</v>
+        <v>5461</v>
       </c>
       <c r="C2" t="n">
-        <v>12014</v>
+        <v>4137</v>
       </c>
       <c r="D2" t="n">
-        <v>20442</v>
+        <v>35550</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3550</v>
+        <v>3337</v>
       </c>
       <c r="C3" t="n">
-        <v>7481</v>
+        <v>3805</v>
       </c>
       <c r="D3" t="n">
-        <v>14225</v>
+        <v>17938</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2819</v>
+        <v>2676</v>
       </c>
       <c r="C4" t="n">
-        <v>6953</v>
+        <v>4494</v>
       </c>
       <c r="D4" t="n">
-        <v>8021</v>
+        <v>8585</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1723</v>
+        <v>1777</v>
       </c>
       <c r="C5" t="n">
-        <v>5662</v>
+        <v>4131</v>
       </c>
       <c r="D5" t="n">
-        <v>3340</v>
+        <v>3192</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>951</v>
+        <v>971</v>
       </c>
       <c r="C6" t="n">
-        <v>3530</v>
+        <v>3395</v>
       </c>
       <c r="D6" t="n">
-        <v>1372</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>456</v>
+        <v>448</v>
       </c>
       <c r="C7" t="n">
-        <v>1785</v>
+        <v>2200</v>
       </c>
       <c r="D7" t="n">
-        <v>684</v>
+        <v>661</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>175</v>
+        <v>164</v>
       </c>
       <c r="C8" t="n">
-        <v>781</v>
+        <v>1090</v>
       </c>
       <c r="D8" t="n">
-        <v>435</v>
+        <v>429</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C9" t="n">
-        <v>336</v>
+        <v>448</v>
       </c>
       <c r="D9" t="n">
-        <v>307</v>
+        <v>301</v>
       </c>
     </row>
     <row r="10">
@@ -895,10 +895,10 @@
         <v>38</v>
       </c>
       <c r="C10" t="n">
-        <v>208</v>
+        <v>224</v>
       </c>
       <c r="D10" t="n">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="11">
@@ -909,7 +909,7 @@
         <v>26</v>
       </c>
       <c r="C11" t="n">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D11" t="n">
         <v>201</v>
@@ -923,7 +923,7 @@
         <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D12" t="n">
         <v>162</v>
@@ -965,7 +965,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D15" t="n">
         <v>82</v>
@@ -982,7 +982,7 @@
         <v>46</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17">
@@ -996,7 +996,7 @@
         <v>38</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -1021,7 +1021,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D19" t="n">
         <v>27</v>
@@ -1035,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1049,7 +1049,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D21" t="n">
         <v>8</v>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7467</v>
+        <v>5830</v>
       </c>
       <c r="C2" t="n">
-        <v>13690</v>
+        <v>11943</v>
       </c>
       <c r="D2" t="n">
-        <v>34899</v>
+        <v>37861</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3932</v>
+        <v>3453</v>
       </c>
       <c r="C3" t="n">
-        <v>8347</v>
+        <v>3488</v>
       </c>
       <c r="D3" t="n">
-        <v>14087</v>
+        <v>19015</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2674</v>
+        <v>2528</v>
       </c>
       <c r="C4" t="n">
-        <v>6984</v>
+        <v>4039</v>
       </c>
       <c r="D4" t="n">
-        <v>8653</v>
+        <v>9678</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1923</v>
+        <v>1907</v>
       </c>
       <c r="C5" t="n">
-        <v>6126</v>
+        <v>4169</v>
       </c>
       <c r="D5" t="n">
-        <v>3957</v>
+        <v>3923</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1167</v>
+        <v>1189</v>
       </c>
       <c r="C6" t="n">
-        <v>4383</v>
+        <v>3687</v>
       </c>
       <c r="D6" t="n">
-        <v>1623</v>
+        <v>1499</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>590</v>
+        <v>601</v>
       </c>
       <c r="C7" t="n">
-        <v>2536</v>
+        <v>2692</v>
       </c>
       <c r="D7" t="n">
-        <v>778</v>
+        <v>740</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>254</v>
+        <v>244</v>
       </c>
       <c r="C8" t="n">
-        <v>1186</v>
+        <v>1557</v>
       </c>
       <c r="D8" t="n">
-        <v>460</v>
+        <v>452</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="C9" t="n">
-        <v>511</v>
+        <v>701</v>
       </c>
       <c r="D9" t="n">
-        <v>321</v>
+        <v>315</v>
       </c>
     </row>
     <row r="10">
@@ -1206,10 +1206,10 @@
         <v>44</v>
       </c>
       <c r="C10" t="n">
-        <v>258</v>
+        <v>311</v>
       </c>
       <c r="D10" t="n">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="11">
@@ -1220,7 +1220,7 @@
         <v>27</v>
       </c>
       <c r="C11" t="n">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="D11" t="n">
         <v>204</v>
@@ -1234,7 +1234,7 @@
         <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="D12" t="n">
         <v>163</v>
@@ -1293,7 +1293,7 @@
         <v>49</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17">
@@ -1304,10 +1304,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -1318,7 +1318,7 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D18" t="n">
         <v>39</v>
@@ -1346,7 +1346,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1360,7 +1360,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D21" t="n">
         <v>9</v>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9017</v>
+        <v>7334</v>
       </c>
       <c r="C2" t="n">
-        <v>17286</v>
+        <v>16733</v>
       </c>
       <c r="D2" t="n">
-        <v>39119</v>
+        <v>31450</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4294</v>
+        <v>3579</v>
       </c>
       <c r="C3" t="n">
-        <v>9276</v>
+        <v>6079</v>
       </c>
       <c r="D3" t="n">
-        <v>15682</v>
+        <v>20059</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2686</v>
+        <v>2466</v>
       </c>
       <c r="C4" t="n">
-        <v>7334</v>
+        <v>3683</v>
       </c>
       <c r="D4" t="n">
-        <v>9172</v>
+        <v>10635</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1970</v>
+        <v>1938</v>
       </c>
       <c r="C5" t="n">
-        <v>6285</v>
+        <v>3988</v>
       </c>
       <c r="D5" t="n">
-        <v>4429</v>
+        <v>4632</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1326</v>
+        <v>1335</v>
       </c>
       <c r="C6" t="n">
-        <v>5031</v>
+        <v>3848</v>
       </c>
       <c r="D6" t="n">
-        <v>1915</v>
+        <v>1790</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>726</v>
+        <v>740</v>
       </c>
       <c r="C7" t="n">
-        <v>3216</v>
+        <v>3054</v>
       </c>
       <c r="D7" t="n">
-        <v>870</v>
+        <v>836</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="C8" t="n">
-        <v>1676</v>
+        <v>1974</v>
       </c>
       <c r="D8" t="n">
-        <v>491</v>
+        <v>479</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="C9" t="n">
-        <v>750</v>
+        <v>1019</v>
       </c>
       <c r="D9" t="n">
-        <v>335</v>
+        <v>329</v>
       </c>
     </row>
     <row r="10">
@@ -1517,10 +1517,10 @@
         <v>54</v>
       </c>
       <c r="C10" t="n">
-        <v>347</v>
+        <v>445</v>
       </c>
       <c r="D10" t="n">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="11">
@@ -1528,10 +1528,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C11" t="n">
-        <v>202</v>
+        <v>225</v>
       </c>
       <c r="D11" t="n">
         <v>206</v>
@@ -1545,7 +1545,7 @@
         <v>19</v>
       </c>
       <c r="C12" t="n">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="D12" t="n">
         <v>164</v>
@@ -1559,7 +1559,7 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D13" t="n">
         <v>129</v>
@@ -1573,7 +1573,7 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D14" t="n">
         <v>99</v>
@@ -1604,7 +1604,7 @@
         <v>52</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17">
@@ -1618,7 +1618,7 @@
         <v>41</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -1657,7 +1657,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1671,7 +1671,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D21" t="n">
         <v>10</v>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8245</v>
+        <v>6668</v>
       </c>
       <c r="C2" t="n">
-        <v>12169</v>
+        <v>11512</v>
       </c>
       <c r="D2" t="n">
-        <v>32047</v>
+        <v>26122</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4922</v>
+        <v>4357</v>
       </c>
       <c r="C3" t="n">
-        <v>13732</v>
+        <v>9265</v>
       </c>
       <c r="D3" t="n">
-        <v>17119</v>
+        <v>21560</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1820</v>
+        <v>1790</v>
       </c>
       <c r="C4" t="n">
-        <v>9905</v>
+        <v>5808</v>
       </c>
       <c r="D4" t="n">
-        <v>9048</v>
+        <v>10144</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1225</v>
+        <v>1233</v>
       </c>
       <c r="C5" t="n">
-        <v>4930</v>
+        <v>3771</v>
       </c>
       <c r="D5" t="n">
-        <v>3067</v>
+        <v>2999</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>670</v>
+        <v>683</v>
       </c>
       <c r="C6" t="n">
-        <v>3151</v>
+        <v>2992</v>
       </c>
       <c r="D6" t="n">
-        <v>852</v>
+        <v>819</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="C7" t="n">
-        <v>1642</v>
+        <v>1934</v>
       </c>
       <c r="D7" t="n">
-        <v>481</v>
+        <v>469</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="C8" t="n">
-        <v>735</v>
+        <v>998</v>
       </c>
       <c r="D8" t="n">
-        <v>328</v>
+        <v>322</v>
       </c>
     </row>
     <row r="9">
@@ -1814,10 +1814,10 @@
         <v>49</v>
       </c>
       <c r="C9" t="n">
-        <v>340</v>
+        <v>436</v>
       </c>
       <c r="D9" t="n">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="10">
@@ -1825,10 +1825,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C10" t="n">
-        <v>197</v>
+        <v>220</v>
       </c>
       <c r="D10" t="n">
         <v>201</v>
@@ -1842,7 +1842,7 @@
         <v>17</v>
       </c>
       <c r="C11" t="n">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D11" t="n">
         <v>160</v>
@@ -1856,7 +1856,7 @@
         <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="D12" t="n">
         <v>126</v>
@@ -1870,7 +1870,7 @@
         <v>5</v>
       </c>
       <c r="C13" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D13" t="n">
         <v>97</v>
@@ -1901,7 +1901,7 @@
         <v>50</v>
       </c>
       <c r="D15" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="16">
@@ -1915,7 +1915,7 @@
         <v>40</v>
       </c>
       <c r="D16" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="17">
@@ -1954,7 +1954,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D19" t="n">
         <v>15</v>
@@ -1968,7 +1968,7 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D20" t="n">
         <v>10</v>
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5004</v>
+        <v>4021</v>
       </c>
       <c r="C2" t="n">
-        <v>5441</v>
+        <v>5724</v>
       </c>
       <c r="D2" t="n">
-        <v>22126</v>
+        <v>18879</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5382</v>
+        <v>4567</v>
       </c>
       <c r="C3" t="n">
-        <v>11854</v>
+        <v>9318</v>
       </c>
       <c r="D3" t="n">
-        <v>18071</v>
+        <v>21145</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2562</v>
+        <v>2384</v>
       </c>
       <c r="C4" t="n">
-        <v>11806</v>
+        <v>7414</v>
       </c>
       <c r="D4" t="n">
-        <v>10108</v>
+        <v>11576</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1368</v>
+        <v>1357</v>
       </c>
       <c r="C5" t="n">
-        <v>7022</v>
+        <v>4694</v>
       </c>
       <c r="D5" t="n">
-        <v>3721</v>
+        <v>3885</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>792</v>
+        <v>813</v>
       </c>
       <c r="C6" t="n">
-        <v>3894</v>
+        <v>3436</v>
       </c>
       <c r="D6" t="n">
-        <v>1058</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="C7" t="n">
-        <v>2170</v>
+        <v>2354</v>
       </c>
       <c r="D7" t="n">
-        <v>525</v>
+        <v>512</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C8" t="n">
-        <v>977</v>
+        <v>1295</v>
       </c>
       <c r="D8" t="n">
-        <v>337</v>
+        <v>331</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C9" t="n">
-        <v>375</v>
+        <v>475</v>
       </c>
       <c r="D9" t="n">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="10">
@@ -2139,7 +2139,7 @@
         <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>215</v>
+        <v>234</v>
       </c>
       <c r="D10" t="n">
         <v>208</v>
@@ -2153,7 +2153,7 @@
         <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D11" t="n">
         <v>167</v>
@@ -2167,7 +2167,7 @@
         <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D12" t="n">
         <v>130</v>
@@ -2198,7 +2198,7 @@
         <v>49</v>
       </c>
       <c r="D14" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="15">
@@ -2212,7 +2212,7 @@
         <v>39</v>
       </c>
       <c r="D15" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="16">
@@ -2251,7 +2251,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D18" t="n">
         <v>14</v>
@@ -2265,7 +2265,7 @@
         <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D19" t="n">
         <v>9</v>
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5611</v>
+        <v>4062</v>
       </c>
       <c r="C2" t="n">
-        <v>9784</v>
+        <v>11536</v>
       </c>
       <c r="D2" t="n">
-        <v>17867</v>
+        <v>17898</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4438</v>
+        <v>3646</v>
       </c>
       <c r="C3" t="n">
-        <v>7936</v>
+        <v>6808</v>
       </c>
       <c r="D3" t="n">
-        <v>17581</v>
+        <v>19415</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3163</v>
+        <v>2854</v>
       </c>
       <c r="C4" t="n">
-        <v>11583</v>
+        <v>8173</v>
       </c>
       <c r="D4" t="n">
-        <v>10926</v>
+        <v>12785</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1641</v>
+        <v>1586</v>
       </c>
       <c r="C5" t="n">
-        <v>9101</v>
+        <v>5849</v>
       </c>
       <c r="D5" t="n">
-        <v>4588</v>
+        <v>4948</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>934</v>
+        <v>949</v>
       </c>
       <c r="C6" t="n">
-        <v>5179</v>
+        <v>3992</v>
       </c>
       <c r="D6" t="n">
-        <v>1427</v>
+        <v>1419</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>421</v>
+        <v>430</v>
       </c>
       <c r="C7" t="n">
-        <v>2899</v>
+        <v>2832</v>
       </c>
       <c r="D7" t="n">
-        <v>592</v>
+        <v>576</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C8" t="n">
-        <v>1442</v>
+        <v>1722</v>
       </c>
       <c r="D8" t="n">
-        <v>360</v>
+        <v>350</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C9" t="n">
-        <v>590</v>
+        <v>776</v>
       </c>
       <c r="D9" t="n">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C10" t="n">
-        <v>270</v>
+        <v>318</v>
       </c>
       <c r="D10" t="n">
-        <v>212</v>
+        <v>210</v>
       </c>
     </row>
     <row r="11">
@@ -2464,7 +2464,7 @@
         <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="D11" t="n">
         <v>170</v>
@@ -2478,7 +2478,7 @@
         <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D12" t="n">
         <v>132</v>
@@ -2492,10 +2492,10 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D13" t="n">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="14">
@@ -2509,7 +2509,7 @@
         <v>53</v>
       </c>
       <c r="D14" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="15">
@@ -2520,7 +2520,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D15" t="n">
         <v>48</v>
@@ -2562,7 +2562,7 @@
         <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D18" t="n">
         <v>13</v>
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3370</v>
+        <v>2435</v>
       </c>
       <c r="C2" t="n">
-        <v>4796</v>
+        <v>5472</v>
       </c>
       <c r="D2" t="n">
-        <v>12614</v>
+        <v>12534</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4577</v>
+        <v>3612</v>
       </c>
       <c r="C3" t="n">
-        <v>8309</v>
+        <v>8162</v>
       </c>
       <c r="D3" t="n">
-        <v>17242</v>
+        <v>18822</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3444</v>
+        <v>3143</v>
       </c>
       <c r="C4" t="n">
-        <v>11368</v>
+        <v>8355</v>
       </c>
       <c r="D4" t="n">
-        <v>11717</v>
+        <v>13630</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1683</v>
+        <v>1657</v>
       </c>
       <c r="C5" t="n">
-        <v>10993</v>
+        <v>7272</v>
       </c>
       <c r="D5" t="n">
-        <v>4693</v>
+        <v>5223</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>751</v>
+        <v>774</v>
       </c>
       <c r="C6" t="n">
-        <v>5925</v>
+        <v>4817</v>
       </c>
       <c r="D6" t="n">
-        <v>1381</v>
+        <v>1378</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C7" t="n">
-        <v>2850</v>
+        <v>3040</v>
       </c>
       <c r="D7" t="n">
-        <v>584</v>
+        <v>574</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C8" t="n">
-        <v>988</v>
+        <v>1266</v>
       </c>
       <c r="D8" t="n">
-        <v>379</v>
+        <v>372</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C9" t="n">
-        <v>264</v>
+        <v>311</v>
       </c>
       <c r="D9" t="n">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="10">
@@ -2761,7 +2761,7 @@
         <v>8</v>
       </c>
       <c r="C10" t="n">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="D10" t="n">
         <v>166</v>
@@ -2775,7 +2775,7 @@
         <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="D11" t="n">
         <v>129</v>
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D12" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="13">
@@ -2806,7 +2806,7 @@
         <v>51</v>
       </c>
       <c r="D13" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="14">
@@ -2817,7 +2817,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D14" t="n">
         <v>47</v>
@@ -2859,7 +2859,7 @@
         <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
         <v>12</v>
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3515</v>
+        <v>3218</v>
       </c>
       <c r="C2" t="n">
-        <v>4322</v>
+        <v>9198</v>
       </c>
       <c r="D2" t="n">
-        <v>14252</v>
+        <v>18216</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3508</v>
+        <v>2687</v>
       </c>
       <c r="C3" t="n">
-        <v>6110</v>
+        <v>6219</v>
       </c>
       <c r="D3" t="n">
-        <v>15684</v>
+        <v>16882</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3408</v>
+        <v>2910</v>
       </c>
       <c r="C4" t="n">
-        <v>9780</v>
+        <v>8092</v>
       </c>
       <c r="D4" t="n">
-        <v>12156</v>
+        <v>14013</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2072</v>
+        <v>1993</v>
       </c>
       <c r="C5" t="n">
-        <v>11028</v>
+        <v>7668</v>
       </c>
       <c r="D5" t="n">
-        <v>5494</v>
+        <v>6274</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>971</v>
+        <v>1003</v>
       </c>
       <c r="C6" t="n">
-        <v>7926</v>
+        <v>5834</v>
       </c>
       <c r="D6" t="n">
-        <v>1776</v>
+        <v>1890</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>272</v>
+        <v>283</v>
       </c>
       <c r="C7" t="n">
-        <v>4049</v>
+        <v>3794</v>
       </c>
       <c r="D7" t="n">
-        <v>677</v>
+        <v>662</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="C8" t="n">
-        <v>1627</v>
+        <v>1916</v>
       </c>
       <c r="D8" t="n">
-        <v>395</v>
+        <v>393</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C9" t="n">
-        <v>484</v>
+        <v>619</v>
       </c>
       <c r="D9" t="n">
-        <v>293</v>
+        <v>290</v>
       </c>
     </row>
     <row r="10">
@@ -3072,10 +3072,10 @@
         <v>8</v>
       </c>
       <c r="C10" t="n">
-        <v>203</v>
+        <v>223</v>
       </c>
       <c r="D10" t="n">
-        <v>172</v>
+        <v>175</v>
       </c>
     </row>
     <row r="11">
@@ -3086,10 +3086,10 @@
         <v>2</v>
       </c>
       <c r="C11" t="n">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D11" t="n">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D12" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D13" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="14">
@@ -3128,7 +3128,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D14" t="n">
         <v>46</v>
@@ -3156,7 +3156,7 @@
         <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D16" t="n">
         <v>20</v>
@@ -3170,7 +3170,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D17" t="n">
         <v>9</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2519</v>
+        <v>2100</v>
       </c>
       <c r="C2" t="n">
-        <v>2885</v>
+        <v>4781</v>
       </c>
       <c r="D2" t="n">
-        <v>10168</v>
+        <v>13339</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3081</v>
+        <v>2500</v>
       </c>
       <c r="C3" t="n">
-        <v>4995</v>
+        <v>6686</v>
       </c>
       <c r="D3" t="n">
-        <v>14695</v>
+        <v>16140</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3129</v>
+        <v>2622</v>
       </c>
       <c r="C4" t="n">
-        <v>8484</v>
+        <v>7419</v>
       </c>
       <c r="D4" t="n">
-        <v>12460</v>
+        <v>14079</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2303</v>
+        <v>2141</v>
       </c>
       <c r="C5" t="n">
-        <v>10708</v>
+        <v>7875</v>
       </c>
       <c r="D5" t="n">
-        <v>6019</v>
+        <v>7020</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1113</v>
+        <v>1171</v>
       </c>
       <c r="C6" t="n">
-        <v>9128</v>
+        <v>6627</v>
       </c>
       <c r="D6" t="n">
-        <v>2075</v>
+        <v>2241</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>242</v>
+        <v>254</v>
       </c>
       <c r="C7" t="n">
-        <v>5161</v>
+        <v>4532</v>
       </c>
       <c r="D7" t="n">
-        <v>765</v>
+        <v>746</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="C8" t="n">
-        <v>2111</v>
+        <v>2396</v>
       </c>
       <c r="D8" t="n">
-        <v>400</v>
+        <v>408</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C9" t="n">
-        <v>520</v>
+        <v>695</v>
       </c>
       <c r="D9" t="n">
-        <v>290</v>
+        <v>286</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>210</v>
+        <v>225</v>
       </c>
       <c r="D10" t="n">
-        <v>175</v>
+        <v>179</v>
       </c>
     </row>
     <row r="11">
@@ -3397,7 +3397,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="D11" t="n">
         <v>135</v>
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D12" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="13">
@@ -3425,7 +3425,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D13" t="n">
         <v>61</v>
@@ -3453,7 +3453,7 @@
         <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D15" t="n">
         <v>19</v>
@@ -3467,7 +3467,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D16" t="n">
         <v>8</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3042</v>
+        <v>2770</v>
       </c>
       <c r="C2" t="n">
-        <v>11919</v>
+        <v>12189</v>
       </c>
       <c r="D2" t="n">
-        <v>16556</v>
+        <v>22611</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2443</v>
+        <v>1989</v>
       </c>
       <c r="C3" t="n">
-        <v>3775</v>
+        <v>5303</v>
       </c>
       <c r="D3" t="n">
-        <v>13271</v>
+        <v>14925</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2705</v>
+        <v>2264</v>
       </c>
       <c r="C4" t="n">
-        <v>6934</v>
+        <v>6962</v>
       </c>
       <c r="D4" t="n">
-        <v>12381</v>
+        <v>13792</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2358</v>
+        <v>2099</v>
       </c>
       <c r="C5" t="n">
-        <v>9652</v>
+        <v>7531</v>
       </c>
       <c r="D5" t="n">
-        <v>6639</v>
+        <v>7755</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1356</v>
+        <v>1383</v>
       </c>
       <c r="C6" t="n">
-        <v>9618</v>
+        <v>7039</v>
       </c>
       <c r="D6" t="n">
-        <v>2503</v>
+        <v>2808</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>439</v>
+        <v>470</v>
       </c>
       <c r="C7" t="n">
-        <v>6519</v>
+        <v>5334</v>
       </c>
       <c r="D7" t="n">
-        <v>890</v>
+        <v>914</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="C8" t="n">
-        <v>3117</v>
+        <v>3106</v>
       </c>
       <c r="D8" t="n">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C9" t="n">
-        <v>987</v>
+        <v>1234</v>
       </c>
       <c r="D9" t="n">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>297</v>
+        <v>360</v>
       </c>
       <c r="D10" t="n">
-        <v>182</v>
+        <v>186</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="D11" t="n">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="12">
@@ -3722,7 +3722,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="D12" t="n">
         <v>92</v>
@@ -3736,7 +3736,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D13" t="n">
         <v>62</v>
@@ -3764,7 +3764,7 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D15" t="n">
         <v>18</v>
@@ -3778,7 +3778,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D16" t="n">
         <v>7</v>
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5589</v>
+        <v>5650</v>
       </c>
       <c r="C2" t="n">
-        <v>6211</v>
+        <v>11824</v>
       </c>
       <c r="D2" t="n">
-        <v>20253</v>
+        <v>9646</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2247</v>
+        <v>2025</v>
       </c>
       <c r="C2" t="n">
-        <v>7152</v>
+        <v>7118</v>
       </c>
       <c r="D2" t="n">
-        <v>12451</v>
+        <v>16822</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3221</v>
+        <v>2646</v>
       </c>
       <c r="C3" t="n">
-        <v>5887</v>
+        <v>7332</v>
       </c>
       <c r="D3" t="n">
-        <v>14485</v>
+        <v>16653</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3538</v>
+        <v>3096</v>
       </c>
       <c r="C4" t="n">
-        <v>10112</v>
+        <v>9532</v>
       </c>
       <c r="D4" t="n">
-        <v>12591</v>
+        <v>14042</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1252</v>
+        <v>1297</v>
       </c>
       <c r="C5" t="n">
-        <v>13753</v>
+        <v>10428</v>
       </c>
       <c r="D5" t="n">
-        <v>5967</v>
+        <v>6987</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>405</v>
+        <v>434</v>
       </c>
       <c r="C6" t="n">
-        <v>7990</v>
+        <v>6468</v>
       </c>
       <c r="D6" t="n">
-        <v>1969</v>
+        <v>2127</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="C7" t="n">
-        <v>3054</v>
+        <v>3043</v>
       </c>
       <c r="D7" t="n">
-        <v>534</v>
+        <v>547</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C8" t="n">
-        <v>967</v>
+        <v>1209</v>
       </c>
       <c r="D8" t="n">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C9" t="n">
-        <v>291</v>
+        <v>352</v>
       </c>
       <c r="D9" t="n">
-        <v>178</v>
+        <v>182</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="D10" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="11">
@@ -4330,7 +4330,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="D11" t="n">
         <v>90</v>
@@ -4344,7 +4344,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D12" t="n">
         <v>60</v>
@@ -4372,7 +4372,7 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D14" t="n">
         <v>17</v>
@@ -4386,7 +4386,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D15" t="n">
         <v>6</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6965</v>
+        <v>6130</v>
       </c>
       <c r="C2" t="n">
-        <v>4512</v>
+        <v>5779</v>
       </c>
       <c r="D2" t="n">
-        <v>23349</v>
+        <v>23236</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2375</v>
+        <v>2401</v>
       </c>
       <c r="C3" t="n">
-        <v>3130</v>
+        <v>5959</v>
       </c>
       <c r="D3" t="n">
-        <v>4041</v>
+        <v>2259</v>
       </c>
     </row>
     <row r="4">
@@ -4557,7 +4557,7 @@
         <v>193</v>
       </c>
       <c r="C5" t="n">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="D5" t="n">
         <v>1161</v>
@@ -4571,7 +4571,7 @@
         <v>200</v>
       </c>
       <c r="C6" t="n">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="D6" t="n">
         <v>816</v>
@@ -4596,7 +4596,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C8" t="n">
         <v>260</v>
@@ -4610,7 +4610,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C9" t="n">
         <v>205</v>
@@ -4697,7 +4697,7 @@
         <v>15</v>
       </c>
       <c r="C15" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D15" t="n">
         <v>118</v>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4296</v>
+        <v>5151</v>
       </c>
       <c r="C2" t="n">
-        <v>9385</v>
+        <v>7007</v>
       </c>
       <c r="D2" t="n">
-        <v>31424</v>
+        <v>26661</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3833</v>
+        <v>3503</v>
       </c>
       <c r="C3" t="n">
-        <v>3373</v>
+        <v>5051</v>
       </c>
       <c r="D3" t="n">
-        <v>6987</v>
+        <v>5616</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1066</v>
+        <v>1077</v>
       </c>
       <c r="C4" t="n">
-        <v>1878</v>
+        <v>3535</v>
       </c>
       <c r="D4" t="n">
-        <v>1995</v>
+        <v>1636</v>
       </c>
     </row>
     <row r="5">
@@ -4868,7 +4868,7 @@
         <v>125</v>
       </c>
       <c r="C5" t="n">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D5" t="n">
         <v>1198</v>
@@ -4893,10 +4893,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C7" t="n">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="D7" t="n">
         <v>584</v>
@@ -4907,7 +4907,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C8" t="n">
         <v>307</v>
@@ -4952,7 +4952,7 @@
         <v>43</v>
       </c>
       <c r="C11" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="D11" t="n">
         <v>270</v>
@@ -4966,7 +4966,7 @@
         <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D12" t="n">
         <v>206</v>
@@ -5022,7 +5022,7 @@
         <v>13</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D16" t="n">
         <v>99</v>
@@ -5036,7 +5036,7 @@
         <v>12</v>
       </c>
       <c r="C17" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D17" t="n">
         <v>77</v>
@@ -5050,7 +5050,7 @@
         <v>11</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D18" t="n">
         <v>59</v>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4520</v>
+        <v>4653</v>
       </c>
       <c r="C2" t="n">
-        <v>7859</v>
+        <v>7819</v>
       </c>
       <c r="D2" t="n">
-        <v>23090</v>
+        <v>33888</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3349</v>
+        <v>3571</v>
       </c>
       <c r="C3" t="n">
-        <v>5714</v>
+        <v>5287</v>
       </c>
       <c r="D3" t="n">
-        <v>10393</v>
+        <v>8578</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2081</v>
+        <v>1918</v>
       </c>
       <c r="C4" t="n">
-        <v>2653</v>
+        <v>4305</v>
       </c>
       <c r="D4" t="n">
-        <v>2892</v>
+        <v>2350</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>489</v>
+        <v>494</v>
       </c>
       <c r="C5" t="n">
-        <v>1124</v>
+        <v>1996</v>
       </c>
       <c r="D5" t="n">
-        <v>1295</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="6">
@@ -5190,10 +5190,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C6" t="n">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="D6" t="n">
         <v>908</v>
@@ -5204,10 +5204,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C7" t="n">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="D7" t="n">
         <v>626</v>
@@ -5218,10 +5218,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C8" t="n">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="D8" t="n">
         <v>454</v>
@@ -5260,10 +5260,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C11" t="n">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D11" t="n">
         <v>280</v>
@@ -5277,7 +5277,7 @@
         <v>31</v>
       </c>
       <c r="C12" t="n">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D12" t="n">
         <v>213</v>
@@ -5291,7 +5291,7 @@
         <v>21</v>
       </c>
       <c r="C13" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D13" t="n">
         <v>173</v>
@@ -5322,7 +5322,7 @@
         <v>77</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="16">
@@ -5333,10 +5333,10 @@
         <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D16" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17">
@@ -5347,7 +5347,7 @@
         <v>11</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D17" t="n">
         <v>78</v>
@@ -5375,7 +5375,7 @@
         <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D19" t="n">
         <v>41</v>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5318</v>
+        <v>6166</v>
       </c>
       <c r="C2" t="n">
-        <v>11548</v>
+        <v>5531</v>
       </c>
       <c r="D2" t="n">
-        <v>19212</v>
+        <v>33930</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3204</v>
+        <v>3355</v>
       </c>
       <c r="C3" t="n">
-        <v>5934</v>
+        <v>5724</v>
       </c>
       <c r="D3" t="n">
-        <v>11591</v>
+        <v>11821</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2287</v>
+        <v>2314</v>
       </c>
       <c r="C4" t="n">
-        <v>4243</v>
+        <v>4733</v>
       </c>
       <c r="D4" t="n">
-        <v>4172</v>
+        <v>3414</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1055</v>
+        <v>979</v>
       </c>
       <c r="C5" t="n">
-        <v>1893</v>
+        <v>3110</v>
       </c>
       <c r="D5" t="n">
-        <v>1519</v>
+        <v>1373</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="C6" t="n">
-        <v>707</v>
+        <v>1145</v>
       </c>
       <c r="D6" t="n">
-        <v>962</v>
+        <v>950</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C7" t="n">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="D7" t="n">
-        <v>660</v>
+        <v>666</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C8" t="n">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="D8" t="n">
-        <v>478</v>
+        <v>471</v>
       </c>
     </row>
     <row r="9">
@@ -5546,7 +5546,7 @@
         <v>97</v>
       </c>
       <c r="C9" t="n">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="D9" t="n">
         <v>380</v>
@@ -5560,7 +5560,7 @@
         <v>70</v>
       </c>
       <c r="C10" t="n">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D10" t="n">
         <v>342</v>
@@ -5571,10 +5571,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C11" t="n">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D11" t="n">
         <v>286</v>
@@ -5585,10 +5585,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C12" t="n">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="D12" t="n">
         <v>217</v>
@@ -5602,7 +5602,7 @@
         <v>22</v>
       </c>
       <c r="C13" t="n">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="D13" t="n">
         <v>176</v>
@@ -5619,7 +5619,7 @@
         <v>100</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="15">
@@ -5630,7 +5630,7 @@
         <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D15" t="n">
         <v>122</v>
@@ -5647,7 +5647,7 @@
         <v>72</v>
       </c>
       <c r="D16" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="17">
@@ -5658,7 +5658,7 @@
         <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D17" t="n">
         <v>78</v>
@@ -5672,7 +5672,7 @@
         <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D18" t="n">
         <v>60</v>
@@ -5686,10 +5686,10 @@
         <v>9</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="20">
@@ -5700,7 +5700,7 @@
         <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D20" t="n">
         <v>24</v>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6753</v>
+        <v>6298</v>
       </c>
       <c r="C2" t="n">
-        <v>10798</v>
+        <v>6506</v>
       </c>
       <c r="D2" t="n">
-        <v>27149</v>
+        <v>24938</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3072</v>
+        <v>3398</v>
       </c>
       <c r="C3" t="n">
-        <v>7211</v>
+        <v>4613</v>
       </c>
       <c r="D3" t="n">
-        <v>11228</v>
+        <v>13605</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1706</v>
+        <v>1738</v>
       </c>
       <c r="C4" t="n">
-        <v>4239</v>
+        <v>4311</v>
       </c>
       <c r="D4" t="n">
-        <v>4709</v>
+        <v>4123</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>865</v>
+        <v>853</v>
       </c>
       <c r="C5" t="n">
-        <v>2276</v>
+        <v>2869</v>
       </c>
       <c r="D5" t="n">
-        <v>1552</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>311</v>
+        <v>291</v>
       </c>
       <c r="C6" t="n">
-        <v>866</v>
+        <v>1404</v>
       </c>
       <c r="D6" t="n">
-        <v>804</v>
+        <v>767</v>
       </c>
     </row>
     <row r="7">
@@ -5829,10 +5829,10 @@
         <v>91</v>
       </c>
       <c r="C7" t="n">
-        <v>336</v>
+        <v>468</v>
       </c>
       <c r="D7" t="n">
-        <v>515</v>
+        <v>522</v>
       </c>
     </row>
     <row r="8">
@@ -5846,7 +5846,7 @@
         <v>221</v>
       </c>
       <c r="D8" t="n">
-        <v>360</v>
+        <v>352</v>
       </c>
     </row>
     <row r="9">
@@ -5860,7 +5860,7 @@
         <v>197</v>
       </c>
       <c r="D9" t="n">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C10" t="n">
         <v>149</v>
       </c>
       <c r="D10" t="n">
-        <v>235</v>
+        <v>233</v>
       </c>
     </row>
     <row r="11">
@@ -5885,7 +5885,7 @@
         <v>21</v>
       </c>
       <c r="C11" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D11" t="n">
         <v>195</v>
@@ -5896,10 +5896,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C12" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D12" t="n">
         <v>147</v>
@@ -5927,7 +5927,7 @@
         <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D14" t="n">
         <v>96</v>
@@ -5941,7 +5941,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D15" t="n">
         <v>79</v>
@@ -5958,7 +5958,7 @@
         <v>38</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17">
@@ -5983,7 +5983,7 @@
         <v>2</v>
       </c>
       <c r="C18" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D18" t="n">
         <v>38</v>
@@ -5997,7 +5997,7 @@
         <v>2</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D19" t="n">
         <v>26</v>
@@ -6025,7 +6025,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D21" t="n">
         <v>5</v>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6112</v>
+        <v>4953</v>
       </c>
       <c r="C2" t="n">
-        <v>8617</v>
+        <v>5715</v>
       </c>
       <c r="D2" t="n">
-        <v>24265</v>
+        <v>33027</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4065</v>
+        <v>4009</v>
       </c>
       <c r="C3" t="n">
-        <v>8003</v>
+        <v>4909</v>
       </c>
       <c r="D3" t="n">
-        <v>13076</v>
+        <v>14507</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2087</v>
+        <v>2245</v>
       </c>
       <c r="C4" t="n">
-        <v>5948</v>
+        <v>4401</v>
       </c>
       <c r="D4" t="n">
-        <v>5834</v>
+        <v>5909</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1134</v>
+        <v>1150</v>
       </c>
       <c r="C5" t="n">
-        <v>3378</v>
+        <v>3639</v>
       </c>
       <c r="D5" t="n">
-        <v>2141</v>
+        <v>1838</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>543</v>
+        <v>520</v>
       </c>
       <c r="C6" t="n">
-        <v>1654</v>
+        <v>2202</v>
       </c>
       <c r="D6" t="n">
-        <v>936</v>
+        <v>870</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="C7" t="n">
-        <v>631</v>
+        <v>976</v>
       </c>
       <c r="D7" t="n">
-        <v>558</v>
+        <v>562</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C8" t="n">
-        <v>282</v>
+        <v>354</v>
       </c>
       <c r="D8" t="n">
-        <v>385</v>
+        <v>374</v>
       </c>
     </row>
     <row r="9">
@@ -6182,10 +6182,10 @@
         <v>33</v>
       </c>
       <c r="C10" t="n">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="D10" t="n">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="11">
@@ -6193,10 +6193,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C11" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D11" t="n">
         <v>199</v>
@@ -6210,7 +6210,7 @@
         <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D12" t="n">
         <v>153</v>
@@ -6221,10 +6221,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C13" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D13" t="n">
         <v>119</v>
@@ -6269,7 +6269,7 @@
         <v>40</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17">
@@ -6294,7 +6294,7 @@
         <v>2</v>
       </c>
       <c r="C18" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D18" t="n">
         <v>39</v>
@@ -6308,7 +6308,7 @@
         <v>1</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D19" t="n">
         <v>26</v>
@@ -6336,7 +6336,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D21" t="n">
         <v>6</v>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4465</v>
+        <v>4495</v>
       </c>
       <c r="C2" t="n">
-        <v>9956</v>
+        <v>4047</v>
       </c>
       <c r="D2" t="n">
-        <v>22669</v>
+        <v>35464</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4147</v>
+        <v>3678</v>
       </c>
       <c r="C3" t="n">
-        <v>7225</v>
+        <v>4632</v>
       </c>
       <c r="D3" t="n">
-        <v>13924</v>
+        <v>16300</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2604</v>
+        <v>2672</v>
       </c>
       <c r="C4" t="n">
-        <v>6968</v>
+        <v>4545</v>
       </c>
       <c r="D4" t="n">
-        <v>7047</v>
+        <v>7240</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1412</v>
+        <v>1464</v>
       </c>
       <c r="C5" t="n">
-        <v>4689</v>
+        <v>3972</v>
       </c>
       <c r="D5" t="n">
-        <v>2749</v>
+        <v>2524</v>
       </c>
     </row>
     <row r="6">
@@ -6437,10 +6437,10 @@
         <v>752</v>
       </c>
       <c r="C6" t="n">
-        <v>2512</v>
+        <v>2922</v>
       </c>
       <c r="D6" t="n">
-        <v>1122</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>317</v>
+        <v>298</v>
       </c>
       <c r="C7" t="n">
-        <v>1162</v>
+        <v>1590</v>
       </c>
       <c r="D7" t="n">
-        <v>618</v>
+        <v>610</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="C8" t="n">
-        <v>456</v>
+        <v>664</v>
       </c>
       <c r="D8" t="n">
-        <v>406</v>
+        <v>401</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C9" t="n">
-        <v>243</v>
+        <v>278</v>
       </c>
       <c r="D9" t="n">
-        <v>297</v>
+        <v>291</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C10" t="n">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="D10" t="n">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="11">
@@ -6504,10 +6504,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C11" t="n">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="D11" t="n">
         <v>200</v>
@@ -6521,7 +6521,7 @@
         <v>16</v>
       </c>
       <c r="C12" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D12" t="n">
         <v>158</v>
@@ -6532,7 +6532,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C13" t="n">
         <v>89</v>
@@ -6549,7 +6549,7 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D14" t="n">
         <v>99</v>
@@ -6580,7 +6580,7 @@
         <v>43</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17">
@@ -6594,7 +6594,7 @@
         <v>37</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -6619,10 +6619,10 @@
         <v>1</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20">
@@ -6647,7 +6647,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D21" t="n">
         <v>7</v>

--- a/output/yearly_population_iteration_60_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_60_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5461</v>
+        <v>8965</v>
       </c>
       <c r="C2" t="n">
-        <v>4137</v>
+        <v>8386</v>
       </c>
       <c r="D2" t="n">
-        <v>35550</v>
+        <v>25610</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3337</v>
+        <v>5304</v>
       </c>
       <c r="C3" t="n">
-        <v>3805</v>
+        <v>5427</v>
       </c>
       <c r="D3" t="n">
-        <v>17938</v>
+        <v>11572</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2676</v>
+        <v>3654</v>
       </c>
       <c r="C4" t="n">
-        <v>4494</v>
+        <v>5536</v>
       </c>
       <c r="D4" t="n">
-        <v>8585</v>
+        <v>6159</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1777</v>
+        <v>2234</v>
       </c>
       <c r="C5" t="n">
-        <v>4131</v>
+        <v>5271</v>
       </c>
       <c r="D5" t="n">
-        <v>3192</v>
+        <v>2514</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>971</v>
+        <v>1197</v>
       </c>
       <c r="C6" t="n">
-        <v>3395</v>
+        <v>4031</v>
       </c>
       <c r="D6" t="n">
-        <v>1248</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>448</v>
+        <v>542</v>
       </c>
       <c r="C7" t="n">
-        <v>2200</v>
+        <v>2579</v>
       </c>
       <c r="D7" t="n">
-        <v>661</v>
+        <v>652</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>164</v>
+        <v>197</v>
       </c>
       <c r="C8" t="n">
-        <v>1090</v>
+        <v>1281</v>
       </c>
       <c r="D8" t="n">
-        <v>429</v>
+        <v>421</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="C9" t="n">
-        <v>448</v>
+        <v>476</v>
       </c>
       <c r="D9" t="n">
-        <v>301</v>
+        <v>304</v>
       </c>
     </row>
     <row r="10">
@@ -898,7 +898,7 @@
         <v>224</v>
       </c>
       <c r="D10" t="n">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="11">
@@ -909,7 +909,7 @@
         <v>26</v>
       </c>
       <c r="C11" t="n">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="D11" t="n">
         <v>201</v>
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C12" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D12" t="n">
-        <v>162</v>
+        <v>158</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D13" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="14">
@@ -951,10 +951,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15">
@@ -962,7 +962,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C15" t="n">
         <v>58</v>
@@ -979,10 +979,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -993,7 +993,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D17" t="n">
         <v>51</v>
@@ -1007,10 +1007,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -1024,7 +1024,7 @@
         <v>30</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20">
@@ -1035,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5830</v>
+        <v>9225</v>
       </c>
       <c r="C2" t="n">
-        <v>11943</v>
+        <v>15376</v>
       </c>
       <c r="D2" t="n">
-        <v>37861</v>
+        <v>20582</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3453</v>
+        <v>5553</v>
       </c>
       <c r="C3" t="n">
-        <v>3488</v>
+        <v>5914</v>
       </c>
       <c r="D3" t="n">
-        <v>19015</v>
+        <v>12609</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2528</v>
+        <v>3692</v>
       </c>
       <c r="C4" t="n">
-        <v>4039</v>
+        <v>5318</v>
       </c>
       <c r="D4" t="n">
-        <v>9678</v>
+        <v>6744</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1907</v>
+        <v>2483</v>
       </c>
       <c r="C5" t="n">
-        <v>4169</v>
+        <v>5278</v>
       </c>
       <c r="D5" t="n">
-        <v>3923</v>
+        <v>2997</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1189</v>
+        <v>1482</v>
       </c>
       <c r="C6" t="n">
-        <v>3687</v>
+        <v>4478</v>
       </c>
       <c r="D6" t="n">
-        <v>1499</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>601</v>
+        <v>717</v>
       </c>
       <c r="C7" t="n">
-        <v>2692</v>
+        <v>3189</v>
       </c>
       <c r="D7" t="n">
-        <v>740</v>
+        <v>718</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>244</v>
+        <v>292</v>
       </c>
       <c r="C8" t="n">
-        <v>1557</v>
+        <v>1789</v>
       </c>
       <c r="D8" t="n">
-        <v>452</v>
+        <v>444</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>91</v>
+        <v>104</v>
       </c>
       <c r="C9" t="n">
-        <v>701</v>
+        <v>786</v>
       </c>
       <c r="D9" t="n">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C10" t="n">
-        <v>311</v>
+        <v>320</v>
       </c>
       <c r="D10" t="n">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="11">
@@ -1220,7 +1220,7 @@
         <v>27</v>
       </c>
       <c r="C11" t="n">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="D11" t="n">
         <v>204</v>
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D12" t="n">
-        <v>163</v>
+        <v>159</v>
       </c>
     </row>
     <row r="13">
@@ -1245,10 +1245,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D13" t="n">
         <v>127</v>
@@ -1262,10 +1262,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15">
@@ -1273,10 +1273,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D15" t="n">
         <v>82</v>
@@ -1287,13 +1287,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C16" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -1304,7 +1304,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D17" t="n">
         <v>51</v>
@@ -1318,10 +1318,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20">
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7334</v>
+        <v>12618</v>
       </c>
       <c r="C2" t="n">
-        <v>16733</v>
+        <v>17949</v>
       </c>
       <c r="D2" t="n">
-        <v>31450</v>
+        <v>19168</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3579</v>
+        <v>5732</v>
       </c>
       <c r="C3" t="n">
-        <v>6079</v>
+        <v>8525</v>
       </c>
       <c r="D3" t="n">
-        <v>20059</v>
+        <v>12758</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2466</v>
+        <v>3731</v>
       </c>
       <c r="C4" t="n">
-        <v>3683</v>
+        <v>5453</v>
       </c>
       <c r="D4" t="n">
-        <v>10635</v>
+        <v>7383</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1938</v>
+        <v>2606</v>
       </c>
       <c r="C5" t="n">
-        <v>3988</v>
+        <v>5133</v>
       </c>
       <c r="D5" t="n">
-        <v>4632</v>
+        <v>3380</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1335</v>
+        <v>1688</v>
       </c>
       <c r="C6" t="n">
-        <v>3848</v>
+        <v>4703</v>
       </c>
       <c r="D6" t="n">
-        <v>1790</v>
+        <v>1527</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>740</v>
+        <v>895</v>
       </c>
       <c r="C7" t="n">
-        <v>3054</v>
+        <v>3649</v>
       </c>
       <c r="D7" t="n">
-        <v>836</v>
+        <v>780</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>333</v>
+        <v>394</v>
       </c>
       <c r="C8" t="n">
-        <v>1974</v>
+        <v>2309</v>
       </c>
       <c r="D8" t="n">
-        <v>479</v>
+        <v>474</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>128</v>
+        <v>149</v>
       </c>
       <c r="C9" t="n">
-        <v>1019</v>
+        <v>1131</v>
       </c>
       <c r="D9" t="n">
-        <v>329</v>
+        <v>324</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="C10" t="n">
-        <v>445</v>
+        <v>476</v>
       </c>
       <c r="D10" t="n">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="11">
@@ -1531,10 +1531,10 @@
         <v>30</v>
       </c>
       <c r="C11" t="n">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="D11" t="n">
-        <v>206</v>
+        <v>204</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="D12" t="n">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D13" t="n">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="14">
@@ -1573,10 +1573,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15">
@@ -1584,10 +1584,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
         <v>82</v>
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C16" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -1612,10 +1612,10 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C17" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D17" t="n">
         <v>51</v>
@@ -1629,10 +1629,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20">
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6668</v>
+        <v>11471</v>
       </c>
       <c r="C2" t="n">
-        <v>11512</v>
+        <v>12636</v>
       </c>
       <c r="D2" t="n">
-        <v>26122</v>
+        <v>15946</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4357</v>
+        <v>6695</v>
       </c>
       <c r="C3" t="n">
-        <v>9265</v>
+        <v>12262</v>
       </c>
       <c r="D3" t="n">
-        <v>21560</v>
+        <v>13974</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1790</v>
+        <v>2407</v>
       </c>
       <c r="C4" t="n">
-        <v>5808</v>
+        <v>7806</v>
       </c>
       <c r="D4" t="n">
-        <v>10144</v>
+        <v>7117</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1233</v>
+        <v>1559</v>
       </c>
       <c r="C5" t="n">
-        <v>3771</v>
+        <v>4608</v>
       </c>
       <c r="D5" t="n">
-        <v>2999</v>
+        <v>2372</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>683</v>
+        <v>826</v>
       </c>
       <c r="C6" t="n">
-        <v>2992</v>
+        <v>3576</v>
       </c>
       <c r="D6" t="n">
-        <v>819</v>
+        <v>764</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>307</v>
+        <v>364</v>
       </c>
       <c r="C7" t="n">
-        <v>1934</v>
+        <v>2262</v>
       </c>
       <c r="D7" t="n">
-        <v>469</v>
+        <v>464</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>118</v>
+        <v>137</v>
       </c>
       <c r="C8" t="n">
-        <v>998</v>
+        <v>1108</v>
       </c>
       <c r="D8" t="n">
-        <v>322</v>
+        <v>317</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C9" t="n">
-        <v>436</v>
+        <v>466</v>
       </c>
       <c r="D9" t="n">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="10">
@@ -1828,10 +1828,10 @@
         <v>27</v>
       </c>
       <c r="C10" t="n">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="D10" t="n">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C11" t="n">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="D11" t="n">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C12" t="n">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D12" t="n">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="13">
@@ -1870,10 +1870,10 @@
         <v>5</v>
       </c>
       <c r="C13" t="n">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D13" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="14">
@@ -1881,10 +1881,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C14" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D14" t="n">
         <v>80</v>
@@ -1895,13 +1895,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C15" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D15" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="16">
@@ -1909,10 +1909,10 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D16" t="n">
         <v>49</v>
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D17" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D18" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="19">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4021</v>
+        <v>6745</v>
       </c>
       <c r="C2" t="n">
-        <v>5724</v>
+        <v>5527</v>
       </c>
       <c r="D2" t="n">
-        <v>18879</v>
+        <v>12616</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4567</v>
+        <v>7400</v>
       </c>
       <c r="C3" t="n">
-        <v>9318</v>
+        <v>11309</v>
       </c>
       <c r="D3" t="n">
-        <v>21145</v>
+        <v>13443</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2384</v>
+        <v>3461</v>
       </c>
       <c r="C4" t="n">
-        <v>7414</v>
+        <v>9836</v>
       </c>
       <c r="D4" t="n">
-        <v>11576</v>
+        <v>8024</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1357</v>
+        <v>1739</v>
       </c>
       <c r="C5" t="n">
-        <v>4694</v>
+        <v>5992</v>
       </c>
       <c r="D5" t="n">
-        <v>3885</v>
+        <v>2892</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>813</v>
+        <v>979</v>
       </c>
       <c r="C6" t="n">
-        <v>3436</v>
+        <v>4097</v>
       </c>
       <c r="D6" t="n">
-        <v>1021</v>
+        <v>916</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>286</v>
+        <v>336</v>
       </c>
       <c r="C7" t="n">
-        <v>2354</v>
+        <v>2795</v>
       </c>
       <c r="D7" t="n">
-        <v>512</v>
+        <v>504</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="C8" t="n">
-        <v>1295</v>
+        <v>1437</v>
       </c>
       <c r="D8" t="n">
-        <v>331</v>
+        <v>327</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C9" t="n">
-        <v>475</v>
+        <v>502</v>
       </c>
       <c r="D9" t="n">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C10" t="n">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="D10" t="n">
-        <v>208</v>
+        <v>205</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C11" t="n">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="D11" t="n">
-        <v>167</v>
+        <v>164</v>
       </c>
     </row>
     <row r="12">
@@ -2167,10 +2167,10 @@
         <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="D12" t="n">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="13">
@@ -2178,10 +2178,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D13" t="n">
         <v>99</v>
@@ -2192,13 +2192,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D14" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="15">
@@ -2209,7 +2209,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D15" t="n">
         <v>48</v>
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D16" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D17" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="18">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4062</v>
+        <v>6853</v>
       </c>
       <c r="C2" t="n">
-        <v>11536</v>
+        <v>9926</v>
       </c>
       <c r="D2" t="n">
-        <v>17898</v>
+        <v>16941</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3646</v>
+        <v>5995</v>
       </c>
       <c r="C3" t="n">
-        <v>6808</v>
+        <v>7747</v>
       </c>
       <c r="D3" t="n">
-        <v>19415</v>
+        <v>12556</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2854</v>
+        <v>4379</v>
       </c>
       <c r="C4" t="n">
-        <v>8173</v>
+        <v>10324</v>
       </c>
       <c r="D4" t="n">
-        <v>12785</v>
+        <v>8535</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1586</v>
+        <v>2151</v>
       </c>
       <c r="C5" t="n">
-        <v>5849</v>
+        <v>7659</v>
       </c>
       <c r="D5" t="n">
-        <v>4948</v>
+        <v>3592</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>949</v>
+        <v>1170</v>
       </c>
       <c r="C6" t="n">
-        <v>3992</v>
+        <v>4859</v>
       </c>
       <c r="D6" t="n">
-        <v>1419</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>430</v>
+        <v>507</v>
       </c>
       <c r="C7" t="n">
-        <v>2832</v>
+        <v>3357</v>
       </c>
       <c r="D7" t="n">
-        <v>576</v>
+        <v>555</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>144</v>
+        <v>164</v>
       </c>
       <c r="C8" t="n">
-        <v>1722</v>
+        <v>1969</v>
       </c>
       <c r="D8" t="n">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C9" t="n">
-        <v>776</v>
+        <v>836</v>
       </c>
       <c r="D9" t="n">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C10" t="n">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="D10" t="n">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C11" t="n">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="D11" t="n">
-        <v>170</v>
+        <v>167</v>
       </c>
     </row>
     <row r="12">
@@ -2478,10 +2478,10 @@
         <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="D12" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="13">
@@ -2489,13 +2489,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D13" t="n">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14">
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D14" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="15">
@@ -2520,10 +2520,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D15" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
+        <v>34</v>
+      </c>
+      <c r="D16" t="n">
         <v>35</v>
-      </c>
-      <c r="D16" t="n">
-        <v>36</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D17" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="18">
@@ -2562,7 +2562,7 @@
         <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D18" t="n">
         <v>13</v>
@@ -2576,7 +2576,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
         <v>6</v>
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2435</v>
+        <v>4153</v>
       </c>
       <c r="C2" t="n">
-        <v>5472</v>
+        <v>4859</v>
       </c>
       <c r="D2" t="n">
-        <v>12534</v>
+        <v>11951</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3612</v>
+        <v>6026</v>
       </c>
       <c r="C3" t="n">
-        <v>8162</v>
+        <v>8228</v>
       </c>
       <c r="D3" t="n">
-        <v>18822</v>
+        <v>12715</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3143</v>
+        <v>4730</v>
       </c>
       <c r="C4" t="n">
-        <v>8355</v>
+        <v>10333</v>
       </c>
       <c r="D4" t="n">
-        <v>13630</v>
+        <v>9062</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1657</v>
+        <v>2177</v>
       </c>
       <c r="C5" t="n">
-        <v>7272</v>
+        <v>9396</v>
       </c>
       <c r="D5" t="n">
-        <v>5223</v>
+        <v>3682</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>774</v>
+        <v>922</v>
       </c>
       <c r="C6" t="n">
-        <v>4817</v>
+        <v>5752</v>
       </c>
       <c r="D6" t="n">
-        <v>1378</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>133</v>
+        <v>151</v>
       </c>
       <c r="C7" t="n">
-        <v>3040</v>
+        <v>3508</v>
       </c>
       <c r="D7" t="n">
-        <v>574</v>
+        <v>558</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C8" t="n">
-        <v>1266</v>
+        <v>1378</v>
       </c>
       <c r="D8" t="n">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C9" t="n">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="D9" t="n">
-        <v>283</v>
+        <v>278</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C10" t="n">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="D10" t="n">
-        <v>166</v>
+        <v>163</v>
       </c>
     </row>
     <row r="11">
@@ -2775,10 +2775,10 @@
         <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="D11" t="n">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D12" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="13">
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D13" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14">
@@ -2817,10 +2817,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D14" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
+        <v>33</v>
+      </c>
+      <c r="D15" t="n">
         <v>34</v>
-      </c>
-      <c r="D15" t="n">
-        <v>35</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D16" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="17">
@@ -2859,7 +2859,7 @@
         <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D17" t="n">
         <v>12</v>
@@ -2873,7 +2873,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D18" t="n">
         <v>5</v>
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3218</v>
+        <v>4792</v>
       </c>
       <c r="C2" t="n">
-        <v>9198</v>
+        <v>3795</v>
       </c>
       <c r="D2" t="n">
-        <v>18216</v>
+        <v>11861</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2687</v>
+        <v>4530</v>
       </c>
       <c r="C3" t="n">
-        <v>6219</v>
+        <v>6052</v>
       </c>
       <c r="D3" t="n">
-        <v>16882</v>
+        <v>11783</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2910</v>
+        <v>4559</v>
       </c>
       <c r="C4" t="n">
-        <v>8092</v>
+        <v>9267</v>
       </c>
       <c r="D4" t="n">
-        <v>14013</v>
+        <v>9347</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1993</v>
+        <v>2778</v>
       </c>
       <c r="C5" t="n">
-        <v>7668</v>
+        <v>9596</v>
       </c>
       <c r="D5" t="n">
-        <v>6274</v>
+        <v>4380</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1003</v>
+        <v>1242</v>
       </c>
       <c r="C6" t="n">
-        <v>5834</v>
+        <v>7283</v>
       </c>
       <c r="D6" t="n">
-        <v>1890</v>
+        <v>1459</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>283</v>
+        <v>324</v>
       </c>
       <c r="C7" t="n">
-        <v>3794</v>
+        <v>4376</v>
       </c>
       <c r="D7" t="n">
-        <v>662</v>
+        <v>623</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="C8" t="n">
-        <v>1916</v>
+        <v>2135</v>
       </c>
       <c r="D8" t="n">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="9">
@@ -3058,10 +3058,10 @@
         <v>20</v>
       </c>
       <c r="C9" t="n">
-        <v>619</v>
+        <v>648</v>
       </c>
       <c r="D9" t="n">
-        <v>290</v>
+        <v>286</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C10" t="n">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="D10" t="n">
-        <v>175</v>
+        <v>172</v>
       </c>
     </row>
     <row r="11">
@@ -3086,7 +3086,7 @@
         <v>2</v>
       </c>
       <c r="C11" t="n">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="D11" t="n">
         <v>133</v>
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="D12" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D13" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D14" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D15" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="16">
@@ -3159,7 +3159,7 @@
         <v>57</v>
       </c>
       <c r="D16" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="17">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2100</v>
+        <v>3437</v>
       </c>
       <c r="C2" t="n">
-        <v>4781</v>
+        <v>2915</v>
       </c>
       <c r="D2" t="n">
-        <v>13339</v>
+        <v>8637</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2500</v>
+        <v>4043</v>
       </c>
       <c r="C3" t="n">
-        <v>6686</v>
+        <v>4761</v>
       </c>
       <c r="D3" t="n">
-        <v>16140</v>
+        <v>11169</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2622</v>
+        <v>4188</v>
       </c>
       <c r="C4" t="n">
-        <v>7419</v>
+        <v>8106</v>
       </c>
       <c r="D4" t="n">
-        <v>14079</v>
+        <v>9456</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2141</v>
+        <v>3061</v>
       </c>
       <c r="C5" t="n">
-        <v>7875</v>
+        <v>9654</v>
       </c>
       <c r="D5" t="n">
-        <v>7020</v>
+        <v>4855</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1171</v>
+        <v>1459</v>
       </c>
       <c r="C6" t="n">
-        <v>6627</v>
+        <v>8238</v>
       </c>
       <c r="D6" t="n">
-        <v>2241</v>
+        <v>1694</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>254</v>
+        <v>287</v>
       </c>
       <c r="C7" t="n">
-        <v>4532</v>
+        <v>5258</v>
       </c>
       <c r="D7" t="n">
-        <v>746</v>
+        <v>693</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C8" t="n">
-        <v>2396</v>
+        <v>2695</v>
       </c>
       <c r="D8" t="n">
-        <v>408</v>
+        <v>400</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C9" t="n">
-        <v>695</v>
+        <v>684</v>
       </c>
       <c r="D9" t="n">
-        <v>286</v>
+        <v>284</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C10" t="n">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="D10" t="n">
-        <v>179</v>
+        <v>175</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="D11" t="n">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="D12" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D14" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="15">
@@ -3456,7 +3456,7 @@
         <v>55</v>
       </c>
       <c r="D15" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="16">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2770</v>
+        <v>4067</v>
       </c>
       <c r="C2" t="n">
-        <v>12189</v>
+        <v>8810</v>
       </c>
       <c r="D2" t="n">
-        <v>22611</v>
+        <v>12143</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1989</v>
+        <v>3235</v>
       </c>
       <c r="C3" t="n">
-        <v>5303</v>
+        <v>3676</v>
       </c>
       <c r="D3" t="n">
-        <v>14925</v>
+        <v>10188</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2264</v>
+        <v>3633</v>
       </c>
       <c r="C4" t="n">
-        <v>6962</v>
+        <v>6542</v>
       </c>
       <c r="D4" t="n">
-        <v>13792</v>
+        <v>9398</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2099</v>
+        <v>3114</v>
       </c>
       <c r="C5" t="n">
-        <v>7531</v>
+        <v>8858</v>
       </c>
       <c r="D5" t="n">
-        <v>7755</v>
+        <v>5235</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1383</v>
+        <v>1817</v>
       </c>
       <c r="C6" t="n">
-        <v>7039</v>
+        <v>8688</v>
       </c>
       <c r="D6" t="n">
-        <v>2808</v>
+        <v>2066</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>470</v>
+        <v>554</v>
       </c>
       <c r="C7" t="n">
-        <v>5334</v>
+        <v>6358</v>
       </c>
       <c r="D7" t="n">
-        <v>914</v>
+        <v>803</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="C8" t="n">
-        <v>3106</v>
+        <v>3522</v>
       </c>
       <c r="D8" t="n">
-        <v>440</v>
+        <v>427</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C9" t="n">
-        <v>1234</v>
+        <v>1301</v>
       </c>
       <c r="D9" t="n">
-        <v>295</v>
+        <v>292</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>360</v>
+        <v>349</v>
       </c>
       <c r="D10" t="n">
-        <v>186</v>
+        <v>184</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="D11" t="n">
-        <v>138</v>
+        <v>135</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="D12" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D13" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D14" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="15">
@@ -3767,7 +3767,7 @@
         <v>58</v>
       </c>
       <c r="D15" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="16">
@@ -3778,7 +3778,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D16" t="n">
         <v>7</v>
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5650</v>
+        <v>7405</v>
       </c>
       <c r="C2" t="n">
-        <v>11824</v>
+        <v>13062</v>
       </c>
       <c r="D2" t="n">
-        <v>9646</v>
+        <v>14382</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2025</v>
+        <v>3010</v>
       </c>
       <c r="C2" t="n">
-        <v>7118</v>
+        <v>5215</v>
       </c>
       <c r="D2" t="n">
-        <v>16822</v>
+        <v>9034</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2646</v>
+        <v>4254</v>
       </c>
       <c r="C3" t="n">
-        <v>7332</v>
+        <v>5141</v>
       </c>
       <c r="D3" t="n">
-        <v>16653</v>
+        <v>11182</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3096</v>
+        <v>4705</v>
       </c>
       <c r="C4" t="n">
-        <v>9532</v>
+        <v>9476</v>
       </c>
       <c r="D4" t="n">
-        <v>14042</v>
+        <v>9556</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1297</v>
+        <v>1707</v>
       </c>
       <c r="C5" t="n">
-        <v>10428</v>
+        <v>12594</v>
       </c>
       <c r="D5" t="n">
-        <v>6987</v>
+        <v>4801</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>434</v>
+        <v>511</v>
       </c>
       <c r="C6" t="n">
-        <v>6468</v>
+        <v>7678</v>
       </c>
       <c r="D6" t="n">
-        <v>2127</v>
+        <v>1684</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="C7" t="n">
-        <v>3043</v>
+        <v>3451</v>
       </c>
       <c r="D7" t="n">
-        <v>547</v>
+        <v>512</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C8" t="n">
-        <v>1209</v>
+        <v>1274</v>
       </c>
       <c r="D8" t="n">
-        <v>289</v>
+        <v>286</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C9" t="n">
-        <v>352</v>
+        <v>342</v>
       </c>
       <c r="D9" t="n">
-        <v>182</v>
+        <v>180</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="D10" t="n">
-        <v>135</v>
+        <v>132</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="D11" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D12" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D13" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14">
@@ -4375,7 +4375,7 @@
         <v>56</v>
       </c>
       <c r="D14" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="15">
@@ -4386,7 +4386,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D15" t="n">
         <v>6</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6130</v>
+        <v>7452</v>
       </c>
       <c r="C2" t="n">
-        <v>5779</v>
+        <v>9111</v>
       </c>
       <c r="D2" t="n">
-        <v>23236</v>
+        <v>14300</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2401</v>
+        <v>3145</v>
       </c>
       <c r="C3" t="n">
-        <v>5959</v>
+        <v>6583</v>
       </c>
       <c r="D3" t="n">
-        <v>2259</v>
+        <v>3055</v>
       </c>
     </row>
     <row r="4">
@@ -4557,7 +4557,7 @@
         <v>193</v>
       </c>
       <c r="C5" t="n">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="D5" t="n">
         <v>1161</v>
@@ -4571,7 +4571,7 @@
         <v>200</v>
       </c>
       <c r="C6" t="n">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="D6" t="n">
         <v>816</v>
@@ -4585,7 +4585,7 @@
         <v>145</v>
       </c>
       <c r="C7" t="n">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="D7" t="n">
         <v>538</v>
@@ -4596,7 +4596,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C8" t="n">
         <v>260</v>
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C9" t="n">
         <v>205</v>
       </c>
       <c r="D9" t="n">
-        <v>354</v>
+        <v>357</v>
       </c>
     </row>
     <row r="10">
@@ -4630,7 +4630,7 @@
         <v>180</v>
       </c>
       <c r="D10" t="n">
-        <v>356</v>
+        <v>352</v>
       </c>
     </row>
     <row r="11">
@@ -4697,7 +4697,7 @@
         <v>15</v>
       </c>
       <c r="C15" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D15" t="n">
         <v>118</v>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5151</v>
+        <v>6362</v>
       </c>
       <c r="C2" t="n">
-        <v>7007</v>
+        <v>8252</v>
       </c>
       <c r="D2" t="n">
-        <v>26661</v>
+        <v>19686</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3503</v>
+        <v>4353</v>
       </c>
       <c r="C3" t="n">
-        <v>5051</v>
+        <v>6910</v>
       </c>
       <c r="D3" t="n">
-        <v>5616</v>
+        <v>4719</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1077</v>
+        <v>1400</v>
       </c>
       <c r="C4" t="n">
-        <v>3535</v>
+        <v>3901</v>
       </c>
       <c r="D4" t="n">
-        <v>1636</v>
+        <v>1797</v>
       </c>
     </row>
     <row r="5">
@@ -4868,7 +4868,7 @@
         <v>125</v>
       </c>
       <c r="C5" t="n">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="D5" t="n">
         <v>1198</v>
@@ -4882,7 +4882,7 @@
         <v>185</v>
       </c>
       <c r="C6" t="n">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="D6" t="n">
         <v>859</v>
@@ -4896,7 +4896,7 @@
         <v>160</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>402</v>
       </c>
       <c r="D7" t="n">
         <v>584</v>
@@ -4910,10 +4910,10 @@
         <v>114</v>
       </c>
       <c r="C8" t="n">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="D8" t="n">
-        <v>439</v>
+        <v>443</v>
       </c>
     </row>
     <row r="9">
@@ -4927,7 +4927,7 @@
         <v>232</v>
       </c>
       <c r="D9" t="n">
-        <v>363</v>
+        <v>361</v>
       </c>
     </row>
     <row r="10">
@@ -4941,7 +4941,7 @@
         <v>192</v>
       </c>
       <c r="D10" t="n">
-        <v>352</v>
+        <v>349</v>
       </c>
     </row>
     <row r="11">
@@ -5022,7 +5022,7 @@
         <v>13</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D16" t="n">
         <v>99</v>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4653</v>
+        <v>6133</v>
       </c>
       <c r="C2" t="n">
-        <v>7819</v>
+        <v>6068</v>
       </c>
       <c r="D2" t="n">
-        <v>33888</v>
+        <v>16651</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3571</v>
+        <v>4371</v>
       </c>
       <c r="C3" t="n">
-        <v>5287</v>
+        <v>6615</v>
       </c>
       <c r="D3" t="n">
-        <v>8578</v>
+        <v>6773</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1918</v>
+        <v>2412</v>
       </c>
       <c r="C4" t="n">
-        <v>4305</v>
+        <v>5495</v>
       </c>
       <c r="D4" t="n">
-        <v>2350</v>
+        <v>2303</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>494</v>
+        <v>624</v>
       </c>
       <c r="C5" t="n">
-        <v>1996</v>
+        <v>2196</v>
       </c>
       <c r="D5" t="n">
-        <v>1229</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="6">
@@ -5193,10 +5193,10 @@
         <v>147</v>
       </c>
       <c r="C6" t="n">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="D6" t="n">
-        <v>908</v>
+        <v>897</v>
       </c>
     </row>
     <row r="7">
@@ -5221,10 +5221,10 @@
         <v>124</v>
       </c>
       <c r="C8" t="n">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="D8" t="n">
-        <v>454</v>
+        <v>457</v>
       </c>
     </row>
     <row r="9">
@@ -5235,10 +5235,10 @@
         <v>91</v>
       </c>
       <c r="C9" t="n">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="D9" t="n">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="10">
@@ -5252,7 +5252,7 @@
         <v>210</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="11">
@@ -5266,7 +5266,7 @@
         <v>177</v>
       </c>
       <c r="D11" t="n">
-        <v>280</v>
+        <v>276</v>
       </c>
     </row>
     <row r="12">
@@ -5277,7 +5277,7 @@
         <v>31</v>
       </c>
       <c r="C12" t="n">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="D12" t="n">
         <v>213</v>
@@ -5291,7 +5291,7 @@
         <v>21</v>
       </c>
       <c r="C13" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D13" t="n">
         <v>173</v>
@@ -5347,7 +5347,7 @@
         <v>11</v>
       </c>
       <c r="C17" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D17" t="n">
         <v>78</v>
@@ -5403,7 +5403,7 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D21" t="n">
         <v>5</v>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6166</v>
+        <v>7601</v>
       </c>
       <c r="C2" t="n">
-        <v>5531</v>
+        <v>10718</v>
       </c>
       <c r="D2" t="n">
-        <v>33930</v>
+        <v>22091</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3355</v>
+        <v>4267</v>
       </c>
       <c r="C3" t="n">
-        <v>5724</v>
+        <v>5527</v>
       </c>
       <c r="D3" t="n">
-        <v>11821</v>
+        <v>7797</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2314</v>
+        <v>2863</v>
       </c>
       <c r="C4" t="n">
-        <v>4733</v>
+        <v>5972</v>
       </c>
       <c r="D4" t="n">
-        <v>3414</v>
+        <v>3048</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>979</v>
+        <v>1232</v>
       </c>
       <c r="C5" t="n">
-        <v>3110</v>
+        <v>3828</v>
       </c>
       <c r="D5" t="n">
-        <v>1373</v>
+        <v>1409</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>276</v>
+        <v>328</v>
       </c>
       <c r="C6" t="n">
-        <v>1145</v>
+        <v>1225</v>
       </c>
       <c r="D6" t="n">
-        <v>950</v>
+        <v>936</v>
       </c>
     </row>
     <row r="7">
@@ -5518,10 +5518,10 @@
         <v>144</v>
       </c>
       <c r="C7" t="n">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="D7" t="n">
-        <v>666</v>
+        <v>664</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C8" t="n">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="D8" t="n">
-        <v>471</v>
+        <v>474</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C9" t="n">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="D9" t="n">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="10">
@@ -5560,10 +5560,10 @@
         <v>70</v>
       </c>
       <c r="C10" t="n">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D10" t="n">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="11">
@@ -5577,7 +5577,7 @@
         <v>189</v>
       </c>
       <c r="D11" t="n">
-        <v>286</v>
+        <v>283</v>
       </c>
     </row>
     <row r="12">
@@ -5588,10 +5588,10 @@
         <v>33</v>
       </c>
       <c r="C12" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D12" t="n">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="13">
@@ -5602,10 +5602,10 @@
         <v>22</v>
       </c>
       <c r="C13" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D13" t="n">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="14">
@@ -5616,7 +5616,7 @@
         <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D14" t="n">
         <v>149</v>
@@ -5644,7 +5644,7 @@
         <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D16" t="n">
         <v>100</v>
@@ -5658,7 +5658,7 @@
         <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D17" t="n">
         <v>78</v>
@@ -5672,7 +5672,7 @@
         <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D18" t="n">
         <v>60</v>
@@ -5686,7 +5686,7 @@
         <v>9</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D19" t="n">
         <v>42</v>
@@ -5714,7 +5714,7 @@
         <v>21</v>
       </c>
       <c r="C21" t="n">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D21" t="n">
         <v>7</v>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6298</v>
+        <v>8681</v>
       </c>
       <c r="C2" t="n">
-        <v>6506</v>
+        <v>8374</v>
       </c>
       <c r="D2" t="n">
-        <v>24938</v>
+        <v>23778</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3398</v>
+        <v>4240</v>
       </c>
       <c r="C3" t="n">
-        <v>4613</v>
+        <v>6625</v>
       </c>
       <c r="D3" t="n">
-        <v>13605</v>
+        <v>8757</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1738</v>
+        <v>2200</v>
       </c>
       <c r="C4" t="n">
-        <v>4311</v>
+        <v>4641</v>
       </c>
       <c r="D4" t="n">
-        <v>4123</v>
+        <v>3262</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>853</v>
+        <v>1046</v>
       </c>
       <c r="C5" t="n">
-        <v>2869</v>
+        <v>3586</v>
       </c>
       <c r="D5" t="n">
-        <v>1363</v>
+        <v>1335</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>291</v>
+        <v>360</v>
       </c>
       <c r="C6" t="n">
-        <v>1404</v>
+        <v>1665</v>
       </c>
       <c r="D6" t="n">
-        <v>767</v>
+        <v>763</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c r="C7" t="n">
-        <v>468</v>
+        <v>493</v>
       </c>
       <c r="D7" t="n">
-        <v>522</v>
+        <v>519</v>
       </c>
     </row>
     <row r="8">
@@ -5843,10 +5843,10 @@
         <v>58</v>
       </c>
       <c r="C8" t="n">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="D8" t="n">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="9">
@@ -5857,7 +5857,7 @@
         <v>44</v>
       </c>
       <c r="C9" t="n">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="D9" t="n">
         <v>272</v>
@@ -5885,10 +5885,10 @@
         <v>21</v>
       </c>
       <c r="C11" t="n">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D11" t="n">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="12">
@@ -5899,7 +5899,7 @@
         <v>13</v>
       </c>
       <c r="C12" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D12" t="n">
         <v>147</v>
@@ -5913,10 +5913,10 @@
         <v>9</v>
       </c>
       <c r="C13" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D13" t="n">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="14">
@@ -5941,7 +5941,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D15" t="n">
         <v>79</v>
@@ -5958,7 +5958,7 @@
         <v>38</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -5969,10 +5969,10 @@
         <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="18">
@@ -5980,10 +5980,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D18" t="n">
         <v>38</v>
@@ -5997,7 +5997,7 @@
         <v>2</v>
       </c>
       <c r="C19" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D19" t="n">
         <v>26</v>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4953</v>
+        <v>7937</v>
       </c>
       <c r="C2" t="n">
-        <v>5715</v>
+        <v>5645</v>
       </c>
       <c r="D2" t="n">
-        <v>33027</v>
+        <v>20544</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4009</v>
+        <v>5311</v>
       </c>
       <c r="C3" t="n">
-        <v>4909</v>
+        <v>6566</v>
       </c>
       <c r="D3" t="n">
-        <v>14507</v>
+        <v>10636</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2245</v>
+        <v>2779</v>
       </c>
       <c r="C4" t="n">
-        <v>4401</v>
+        <v>5661</v>
       </c>
       <c r="D4" t="n">
-        <v>5909</v>
+        <v>4270</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1150</v>
+        <v>1439</v>
       </c>
       <c r="C5" t="n">
-        <v>3639</v>
+        <v>4119</v>
       </c>
       <c r="D5" t="n">
-        <v>1838</v>
+        <v>1651</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>520</v>
+        <v>643</v>
       </c>
       <c r="C6" t="n">
-        <v>2202</v>
+        <v>2714</v>
       </c>
       <c r="D6" t="n">
-        <v>870</v>
+        <v>861</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>172</v>
+        <v>204</v>
       </c>
       <c r="C7" t="n">
-        <v>976</v>
+        <v>1135</v>
       </c>
       <c r="D7" t="n">
-        <v>562</v>
+        <v>559</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="C8" t="n">
-        <v>354</v>
+        <v>365</v>
       </c>
       <c r="D8" t="n">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="9">
@@ -6165,10 +6165,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C9" t="n">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="D9" t="n">
         <v>283</v>
@@ -6182,10 +6182,10 @@
         <v>33</v>
       </c>
       <c r="C10" t="n">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="D10" t="n">
-        <v>234</v>
+        <v>237</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C11" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D11" t="n">
-        <v>199</v>
+        <v>196</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C12" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D12" t="n">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="13">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="15">
@@ -6252,7 +6252,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D15" t="n">
         <v>80</v>
@@ -6266,10 +6266,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -6280,10 +6280,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18">
@@ -6294,10 +6294,10 @@
         <v>2</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -6305,10 +6305,10 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C19" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D19" t="n">
         <v>26</v>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4495</v>
+        <v>7821</v>
       </c>
       <c r="C2" t="n">
-        <v>4047</v>
+        <v>7194</v>
       </c>
       <c r="D2" t="n">
-        <v>35464</v>
+        <v>18080</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3678</v>
+        <v>5382</v>
       </c>
       <c r="C3" t="n">
-        <v>4632</v>
+        <v>5284</v>
       </c>
       <c r="D3" t="n">
-        <v>16300</v>
+        <v>11393</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2672</v>
+        <v>3405</v>
       </c>
       <c r="C4" t="n">
-        <v>4545</v>
+        <v>6038</v>
       </c>
       <c r="D4" t="n">
-        <v>7240</v>
+        <v>5260</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1464</v>
+        <v>1833</v>
       </c>
       <c r="C5" t="n">
-        <v>3972</v>
+        <v>4847</v>
       </c>
       <c r="D5" t="n">
-        <v>2524</v>
+        <v>2078</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>752</v>
+        <v>923</v>
       </c>
       <c r="C6" t="n">
-        <v>2922</v>
+        <v>3372</v>
       </c>
       <c r="D6" t="n">
-        <v>1016</v>
+        <v>985</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>298</v>
+        <v>366</v>
       </c>
       <c r="C7" t="n">
-        <v>1590</v>
+        <v>1939</v>
       </c>
       <c r="D7" t="n">
-        <v>610</v>
+        <v>598</v>
       </c>
     </row>
     <row r="8">
@@ -6462,10 +6462,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>103</v>
+        <v>117</v>
       </c>
       <c r="C8" t="n">
-        <v>664</v>
+        <v>742</v>
       </c>
       <c r="D8" t="n">
         <v>401</v>
@@ -6476,10 +6476,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C9" t="n">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="D9" t="n">
         <v>291</v>
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C10" t="n">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="D10" t="n">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C11" t="n">
         <v>147</v>
       </c>
       <c r="D11" t="n">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="12">
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D12" t="n">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
     <row r="13">
@@ -6535,10 +6535,10 @@
         <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D13" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
         <v>69</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="15">
@@ -6563,7 +6563,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D15" t="n">
         <v>81</v>
@@ -6577,10 +6577,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -6591,7 +6591,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D17" t="n">
         <v>51</v>
@@ -6605,10 +6605,10 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -6619,7 +6619,7 @@
         <v>1</v>
       </c>
       <c r="C19" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D19" t="n">
         <v>26</v>
@@ -6630,7 +6630,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C20" t="n">
         <v>29</v>

--- a/output/yearly_population_iteration_60_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_60_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8965</v>
+        <v>1048</v>
       </c>
       <c r="C2" t="n">
-        <v>8386</v>
+        <v>1968</v>
       </c>
       <c r="D2" t="n">
-        <v>25610</v>
+        <v>18613</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5304</v>
+        <v>2251</v>
       </c>
       <c r="C3" t="n">
-        <v>5427</v>
+        <v>4860</v>
       </c>
       <c r="D3" t="n">
-        <v>11572</v>
+        <v>18108</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3654</v>
+        <v>1550</v>
       </c>
       <c r="C4" t="n">
-        <v>5536</v>
+        <v>6774</v>
       </c>
       <c r="D4" t="n">
-        <v>6159</v>
+        <v>7588</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2234</v>
+        <v>692</v>
       </c>
       <c r="C5" t="n">
-        <v>5271</v>
+        <v>4750</v>
       </c>
       <c r="D5" t="n">
-        <v>2514</v>
+        <v>2145</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1197</v>
+        <v>283</v>
       </c>
       <c r="C6" t="n">
-        <v>4031</v>
+        <v>1797</v>
       </c>
       <c r="D6" t="n">
-        <v>1149</v>
+        <v>757</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>542</v>
+        <v>102</v>
       </c>
       <c r="C7" t="n">
-        <v>2579</v>
+        <v>603</v>
       </c>
       <c r="D7" t="n">
-        <v>652</v>
+        <v>482</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>197</v>
+        <v>74</v>
       </c>
       <c r="C8" t="n">
-        <v>1281</v>
+        <v>336</v>
       </c>
       <c r="D8" t="n">
-        <v>421</v>
+        <v>371</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>70</v>
+        <v>53</v>
       </c>
       <c r="C9" t="n">
-        <v>476</v>
+        <v>283</v>
       </c>
       <c r="D9" t="n">
-        <v>304</v>
+        <v>315</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="C10" t="n">
-        <v>224</v>
+        <v>213</v>
       </c>
       <c r="D10" t="n">
-        <v>243</v>
+        <v>270</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="C11" t="n">
-        <v>161</v>
+        <v>174</v>
       </c>
       <c r="D11" t="n">
-        <v>201</v>
+        <v>211</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>124</v>
+        <v>110</v>
       </c>
       <c r="D12" t="n">
-        <v>158</v>
+        <v>173</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>96</v>
+        <v>77</v>
       </c>
       <c r="D13" t="n">
-        <v>125</v>
+        <v>138</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>89</v>
       </c>
     </row>
     <row r="15">
@@ -962,13 +962,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>72</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>53</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>38</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>21</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>30</v>
+        <v>140</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>97</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9225</v>
+        <v>1258</v>
       </c>
       <c r="C2" t="n">
-        <v>15376</v>
+        <v>7946</v>
       </c>
       <c r="D2" t="n">
-        <v>20582</v>
+        <v>17628</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5553</v>
+        <v>1429</v>
       </c>
       <c r="C3" t="n">
-        <v>5914</v>
+        <v>2903</v>
       </c>
       <c r="D3" t="n">
-        <v>12609</v>
+        <v>16909</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3692</v>
+        <v>1634</v>
       </c>
       <c r="C4" t="n">
-        <v>5318</v>
+        <v>5650</v>
       </c>
       <c r="D4" t="n">
-        <v>6744</v>
+        <v>9276</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2483</v>
+        <v>951</v>
       </c>
       <c r="C5" t="n">
-        <v>5278</v>
+        <v>5700</v>
       </c>
       <c r="D5" t="n">
-        <v>2997</v>
+        <v>3020</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1482</v>
+        <v>423</v>
       </c>
       <c r="C6" t="n">
-        <v>4478</v>
+        <v>3269</v>
       </c>
       <c r="D6" t="n">
-        <v>1319</v>
+        <v>973</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>717</v>
+        <v>158</v>
       </c>
       <c r="C7" t="n">
-        <v>3189</v>
+        <v>1182</v>
       </c>
       <c r="D7" t="n">
-        <v>718</v>
+        <v>520</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>292</v>
+        <v>79</v>
       </c>
       <c r="C8" t="n">
-        <v>1789</v>
+        <v>462</v>
       </c>
       <c r="D8" t="n">
-        <v>444</v>
+        <v>387</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>104</v>
+        <v>56</v>
       </c>
       <c r="C9" t="n">
-        <v>786</v>
+        <v>307</v>
       </c>
       <c r="D9" t="n">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="C10" t="n">
-        <v>320</v>
+        <v>243</v>
       </c>
       <c r="D10" t="n">
-        <v>245</v>
+        <v>275</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="C11" t="n">
-        <v>182</v>
+        <v>192</v>
       </c>
       <c r="D11" t="n">
-        <v>204</v>
+        <v>216</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="D12" t="n">
-        <v>159</v>
+        <v>175</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>104</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
-        <v>127</v>
+        <v>141</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C14" t="n">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>94</v>
       </c>
     </row>
     <row r="15">
@@ -1273,13 +1273,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>71</v>
       </c>
     </row>
     <row r="16">
@@ -1287,13 +1287,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>52</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>36</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>94</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>17</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>30</v>
+        <v>76</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>103</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>12618</v>
+        <v>671</v>
       </c>
       <c r="C2" t="n">
-        <v>17949</v>
+        <v>3259</v>
       </c>
       <c r="D2" t="n">
-        <v>19168</v>
+        <v>11892</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5732</v>
+        <v>1328</v>
       </c>
       <c r="C3" t="n">
-        <v>8525</v>
+        <v>4759</v>
       </c>
       <c r="D3" t="n">
-        <v>12758</v>
+        <v>16541</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3731</v>
+        <v>1755</v>
       </c>
       <c r="C4" t="n">
-        <v>5453</v>
+        <v>5047</v>
       </c>
       <c r="D4" t="n">
-        <v>7383</v>
+        <v>10407</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2606</v>
+        <v>946</v>
       </c>
       <c r="C5" t="n">
-        <v>5133</v>
+        <v>6388</v>
       </c>
       <c r="D5" t="n">
-        <v>3380</v>
+        <v>3430</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1688</v>
+        <v>337</v>
       </c>
       <c r="C6" t="n">
-        <v>4703</v>
+        <v>4118</v>
       </c>
       <c r="D6" t="n">
-        <v>1527</v>
+        <v>984</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>895</v>
+        <v>72</v>
       </c>
       <c r="C7" t="n">
-        <v>3649</v>
+        <v>1135</v>
       </c>
       <c r="D7" t="n">
-        <v>780</v>
+        <v>551</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>394</v>
+        <v>51</v>
       </c>
       <c r="C8" t="n">
-        <v>2309</v>
+        <v>463</v>
       </c>
       <c r="D8" t="n">
-        <v>474</v>
+        <v>431</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>149</v>
+        <v>26</v>
       </c>
       <c r="C9" t="n">
-        <v>1131</v>
+        <v>238</v>
       </c>
       <c r="D9" t="n">
-        <v>324</v>
+        <v>369</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>57</v>
+        <v>14</v>
       </c>
       <c r="C10" t="n">
-        <v>476</v>
+        <v>188</v>
       </c>
       <c r="D10" t="n">
-        <v>250</v>
+        <v>211</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>227</v>
+        <v>129</v>
       </c>
       <c r="D11" t="n">
-        <v>204</v>
+        <v>171</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="C12" t="n">
-        <v>149</v>
+        <v>86</v>
       </c>
       <c r="D12" t="n">
-        <v>162</v>
+        <v>138</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>112</v>
+        <v>68</v>
       </c>
       <c r="D13" t="n">
-        <v>127</v>
+        <v>92</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>87</v>
+        <v>62</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>69</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>50</v>
       </c>
     </row>
     <row r="16">
@@ -1601,10 +1601,10 @@
         <v>2</v>
       </c>
       <c r="C16" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>35</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="C17" t="n">
-        <v>39</v>
+        <v>92</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>16</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>74</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>108</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>11471</v>
+        <v>1167</v>
       </c>
       <c r="C2" t="n">
-        <v>12636</v>
+        <v>3906</v>
       </c>
       <c r="D2" t="n">
-        <v>15946</v>
+        <v>10219</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>6695</v>
+        <v>880</v>
       </c>
       <c r="C3" t="n">
-        <v>12262</v>
+        <v>3515</v>
       </c>
       <c r="D3" t="n">
-        <v>13974</v>
+        <v>14828</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2407</v>
+        <v>1394</v>
       </c>
       <c r="C4" t="n">
-        <v>7806</v>
+        <v>4838</v>
       </c>
       <c r="D4" t="n">
-        <v>7117</v>
+        <v>11150</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1559</v>
+        <v>1157</v>
       </c>
       <c r="C5" t="n">
-        <v>4608</v>
+        <v>5647</v>
       </c>
       <c r="D5" t="n">
-        <v>2372</v>
+        <v>4464</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>826</v>
+        <v>529</v>
       </c>
       <c r="C6" t="n">
-        <v>3576</v>
+        <v>5224</v>
       </c>
       <c r="D6" t="n">
-        <v>764</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>364</v>
+        <v>146</v>
       </c>
       <c r="C7" t="n">
-        <v>2262</v>
+        <v>2472</v>
       </c>
       <c r="D7" t="n">
-        <v>464</v>
+        <v>604</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>137</v>
+        <v>55</v>
       </c>
       <c r="C8" t="n">
-        <v>1108</v>
+        <v>741</v>
       </c>
       <c r="D8" t="n">
-        <v>317</v>
+        <v>446</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="C9" t="n">
-        <v>466</v>
+        <v>326</v>
       </c>
       <c r="D9" t="n">
-        <v>245</v>
+        <v>379</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="C10" t="n">
-        <v>222</v>
+        <v>210</v>
       </c>
       <c r="D10" t="n">
-        <v>199</v>
+        <v>223</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="C11" t="n">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="D11" t="n">
-        <v>158</v>
+        <v>177</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="D12" t="n">
-        <v>124</v>
+        <v>142</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="D13" t="n">
-        <v>96</v>
+        <v>92</v>
       </c>
     </row>
     <row r="14">
@@ -1884,10 +1884,10 @@
         <v>2</v>
       </c>
       <c r="C14" t="n">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="D14" t="n">
-        <v>80</v>
+        <v>68</v>
       </c>
     </row>
     <row r="15">
@@ -1895,13 +1895,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C15" t="n">
+        <v>66</v>
+      </c>
+      <c r="D15" t="n">
         <v>49</v>
-      </c>
-      <c r="D15" t="n">
-        <v>62</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>38</v>
+        <v>90</v>
       </c>
       <c r="D16" t="n">
-        <v>49</v>
+        <v>30</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33</v>
+        <v>100</v>
       </c>
       <c r="D17" t="n">
-        <v>37</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="D18" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>108</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6745</v>
+        <v>583</v>
       </c>
       <c r="C2" t="n">
-        <v>5527</v>
+        <v>2403</v>
       </c>
       <c r="D2" t="n">
-        <v>12616</v>
+        <v>8248</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>7400</v>
+        <v>860</v>
       </c>
       <c r="C3" t="n">
-        <v>11309</v>
+        <v>3314</v>
       </c>
       <c r="D3" t="n">
-        <v>13443</v>
+        <v>13347</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3461</v>
+        <v>1117</v>
       </c>
       <c r="C4" t="n">
-        <v>9836</v>
+        <v>4254</v>
       </c>
       <c r="D4" t="n">
-        <v>8024</v>
+        <v>11483</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1739</v>
+        <v>1209</v>
       </c>
       <c r="C5" t="n">
-        <v>5992</v>
+        <v>5404</v>
       </c>
       <c r="D5" t="n">
-        <v>2892</v>
+        <v>5312</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>979</v>
+        <v>662</v>
       </c>
       <c r="C6" t="n">
-        <v>4097</v>
+        <v>5643</v>
       </c>
       <c r="D6" t="n">
-        <v>916</v>
+        <v>1707</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>336</v>
+        <v>165</v>
       </c>
       <c r="C7" t="n">
-        <v>2795</v>
+        <v>3449</v>
       </c>
       <c r="D7" t="n">
-        <v>504</v>
+        <v>671</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>113</v>
+        <v>52</v>
       </c>
       <c r="C8" t="n">
-        <v>1437</v>
+        <v>1169</v>
       </c>
       <c r="D8" t="n">
-        <v>327</v>
+        <v>480</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="C9" t="n">
-        <v>502</v>
+        <v>421</v>
       </c>
       <c r="D9" t="n">
-        <v>256</v>
+        <v>376</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C10" t="n">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="D10" t="n">
-        <v>205</v>
+        <v>232</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="D11" t="n">
-        <v>164</v>
+        <v>184</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>91</v>
+        <v>108</v>
       </c>
       <c r="D12" t="n">
-        <v>129</v>
+        <v>136</v>
       </c>
     </row>
     <row r="13">
@@ -2181,10 +2181,10 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="D13" t="n">
-        <v>99</v>
+        <v>93</v>
       </c>
     </row>
     <row r="14">
@@ -2192,13 +2192,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>48</v>
+        <v>64</v>
       </c>
       <c r="D14" t="n">
-        <v>60</v>
+        <v>54</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="C15" t="n">
-        <v>37</v>
+        <v>88</v>
       </c>
       <c r="D15" t="n">
-        <v>48</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>32</v>
+        <v>98</v>
       </c>
       <c r="D16" t="n">
-        <v>36</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>105</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6853</v>
+        <v>863</v>
       </c>
       <c r="C2" t="n">
-        <v>9926</v>
+        <v>9329</v>
       </c>
       <c r="D2" t="n">
-        <v>16941</v>
+        <v>13640</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5995</v>
+        <v>628</v>
       </c>
       <c r="C3" t="n">
-        <v>7747</v>
+        <v>2539</v>
       </c>
       <c r="D3" t="n">
-        <v>12556</v>
+        <v>11756</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>4379</v>
+        <v>880</v>
       </c>
       <c r="C4" t="n">
-        <v>10324</v>
+        <v>3746</v>
       </c>
       <c r="D4" t="n">
-        <v>8535</v>
+        <v>11438</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2151</v>
+        <v>1086</v>
       </c>
       <c r="C5" t="n">
-        <v>7659</v>
+        <v>4761</v>
       </c>
       <c r="D5" t="n">
-        <v>3592</v>
+        <v>6098</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1170</v>
+        <v>811</v>
       </c>
       <c r="C6" t="n">
-        <v>4859</v>
+        <v>5483</v>
       </c>
       <c r="D6" t="n">
-        <v>1188</v>
+        <v>2203</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>507</v>
+        <v>310</v>
       </c>
       <c r="C7" t="n">
-        <v>3357</v>
+        <v>4427</v>
       </c>
       <c r="D7" t="n">
-        <v>555</v>
+        <v>806</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>164</v>
+        <v>79</v>
       </c>
       <c r="C8" t="n">
-        <v>1969</v>
+        <v>2096</v>
       </c>
       <c r="D8" t="n">
-        <v>349</v>
+        <v>499</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>55</v>
+        <v>31</v>
       </c>
       <c r="C9" t="n">
-        <v>836</v>
+        <v>703</v>
       </c>
       <c r="D9" t="n">
-        <v>261</v>
+        <v>384</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="C10" t="n">
-        <v>324</v>
+        <v>295</v>
       </c>
       <c r="D10" t="n">
-        <v>209</v>
+        <v>247</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="D11" t="n">
-        <v>167</v>
+        <v>186</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>109</v>
+        <v>124</v>
       </c>
       <c r="D12" t="n">
-        <v>131</v>
+        <v>139</v>
       </c>
     </row>
     <row r="13">
@@ -2489,13 +2489,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="D13" t="n">
-        <v>100</v>
+        <v>96</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="D14" t="n">
-        <v>62</v>
+        <v>55</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C15" t="n">
-        <v>42</v>
+        <v>90</v>
       </c>
       <c r="D15" t="n">
-        <v>47</v>
+        <v>28</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>34</v>
+        <v>100</v>
       </c>
       <c r="D16" t="n">
-        <v>35</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4153</v>
+        <v>579</v>
       </c>
       <c r="C2" t="n">
-        <v>4859</v>
+        <v>4851</v>
       </c>
       <c r="D2" t="n">
-        <v>11951</v>
+        <v>9820</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>6026</v>
+        <v>885</v>
       </c>
       <c r="C3" t="n">
-        <v>8228</v>
+        <v>4635</v>
       </c>
       <c r="D3" t="n">
-        <v>12715</v>
+        <v>12925</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>4730</v>
+        <v>1433</v>
       </c>
       <c r="C4" t="n">
-        <v>10333</v>
+        <v>5244</v>
       </c>
       <c r="D4" t="n">
-        <v>9062</v>
+        <v>11777</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2177</v>
+        <v>829</v>
       </c>
       <c r="C5" t="n">
-        <v>9396</v>
+        <v>7366</v>
       </c>
       <c r="D5" t="n">
-        <v>3682</v>
+        <v>5543</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>922</v>
+        <v>286</v>
       </c>
       <c r="C6" t="n">
-        <v>5752</v>
+        <v>5681</v>
       </c>
       <c r="D6" t="n">
-        <v>1160</v>
+        <v>1794</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>151</v>
+        <v>72</v>
       </c>
       <c r="C7" t="n">
-        <v>3508</v>
+        <v>2054</v>
       </c>
       <c r="D7" t="n">
-        <v>558</v>
+        <v>607</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>50</v>
+        <v>28</v>
       </c>
       <c r="C8" t="n">
-        <v>1378</v>
+        <v>688</v>
       </c>
       <c r="D8" t="n">
-        <v>373</v>
+        <v>376</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="C9" t="n">
-        <v>317</v>
+        <v>289</v>
       </c>
       <c r="D9" t="n">
-        <v>278</v>
+        <v>242</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="D10" t="n">
-        <v>163</v>
+        <v>182</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>106</v>
+        <v>121</v>
       </c>
       <c r="D11" t="n">
-        <v>128</v>
+        <v>136</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="D12" t="n">
-        <v>98</v>
+        <v>94</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="D13" t="n">
-        <v>60</v>
+        <v>53</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>41</v>
+        <v>88</v>
       </c>
       <c r="D14" t="n">
-        <v>46</v>
+        <v>27</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>33</v>
+        <v>98</v>
       </c>
       <c r="D15" t="n">
-        <v>34</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4792</v>
+        <v>340</v>
       </c>
       <c r="C2" t="n">
-        <v>3795</v>
+        <v>2900</v>
       </c>
       <c r="D2" t="n">
-        <v>11861</v>
+        <v>7076</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4530</v>
+        <v>637</v>
       </c>
       <c r="C3" t="n">
-        <v>6052</v>
+        <v>4175</v>
       </c>
       <c r="D3" t="n">
-        <v>11783</v>
+        <v>11551</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>4559</v>
+        <v>982</v>
       </c>
       <c r="C4" t="n">
-        <v>9267</v>
+        <v>4681</v>
       </c>
       <c r="D4" t="n">
-        <v>9347</v>
+        <v>11146</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2778</v>
+        <v>775</v>
       </c>
       <c r="C5" t="n">
-        <v>9596</v>
+        <v>5594</v>
       </c>
       <c r="D5" t="n">
-        <v>4380</v>
+        <v>5801</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1242</v>
+        <v>289</v>
       </c>
       <c r="C6" t="n">
-        <v>7283</v>
+        <v>5327</v>
       </c>
       <c r="D6" t="n">
-        <v>1459</v>
+        <v>1945</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>324</v>
+        <v>64</v>
       </c>
       <c r="C7" t="n">
-        <v>4376</v>
+        <v>2608</v>
       </c>
       <c r="D7" t="n">
-        <v>623</v>
+        <v>601</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>68</v>
+        <v>14</v>
       </c>
       <c r="C8" t="n">
-        <v>2135</v>
+        <v>791</v>
       </c>
       <c r="D8" t="n">
-        <v>392</v>
+        <v>321</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="C9" t="n">
-        <v>648</v>
+        <v>270</v>
       </c>
       <c r="D9" t="n">
-        <v>286</v>
+        <v>194</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>221</v>
+        <v>131</v>
       </c>
       <c r="D10" t="n">
-        <v>172</v>
+        <v>139</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>124</v>
+        <v>77</v>
       </c>
       <c r="D11" t="n">
-        <v>133</v>
+        <v>99</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>78</v>
+        <v>53</v>
       </c>
       <c r="D12" t="n">
-        <v>98</v>
+        <v>62</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D13" t="n">
-        <v>60</v>
+        <v>31</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="D14" t="n">
-        <v>45</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3437</v>
+        <v>424</v>
       </c>
       <c r="C2" t="n">
-        <v>2915</v>
+        <v>4724</v>
       </c>
       <c r="D2" t="n">
-        <v>8637</v>
+        <v>14279</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4043</v>
+        <v>415</v>
       </c>
       <c r="C3" t="n">
-        <v>4761</v>
+        <v>3052</v>
       </c>
       <c r="D3" t="n">
-        <v>11169</v>
+        <v>10003</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>4188</v>
+        <v>720</v>
       </c>
       <c r="C4" t="n">
-        <v>8106</v>
+        <v>4301</v>
       </c>
       <c r="D4" t="n">
-        <v>9456</v>
+        <v>10884</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3061</v>
+        <v>784</v>
       </c>
       <c r="C5" t="n">
-        <v>9654</v>
+        <v>4986</v>
       </c>
       <c r="D5" t="n">
-        <v>4855</v>
+        <v>6599</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1459</v>
+        <v>468</v>
       </c>
       <c r="C6" t="n">
-        <v>8238</v>
+        <v>5457</v>
       </c>
       <c r="D6" t="n">
-        <v>1694</v>
+        <v>2584</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>287</v>
+        <v>144</v>
       </c>
       <c r="C7" t="n">
-        <v>5258</v>
+        <v>3991</v>
       </c>
       <c r="D7" t="n">
-        <v>693</v>
+        <v>818</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>54</v>
+        <v>29</v>
       </c>
       <c r="C8" t="n">
-        <v>2695</v>
+        <v>1653</v>
       </c>
       <c r="D8" t="n">
-        <v>400</v>
+        <v>361</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="C9" t="n">
-        <v>684</v>
+        <v>502</v>
       </c>
       <c r="D9" t="n">
-        <v>284</v>
+        <v>212</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>220</v>
+        <v>189</v>
       </c>
       <c r="D10" t="n">
-        <v>175</v>
+        <v>144</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>122</v>
+        <v>99</v>
       </c>
       <c r="D11" t="n">
-        <v>134</v>
+        <v>103</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="D12" t="n">
-        <v>91</v>
+        <v>65</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="D13" t="n">
-        <v>60</v>
+        <v>33</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="D14" t="n">
-        <v>35</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>55</v>
+        <v>11</v>
       </c>
       <c r="D15" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3484,7 +3484,7 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4067</v>
+        <v>563</v>
       </c>
       <c r="C2" t="n">
-        <v>8810</v>
+        <v>10075</v>
       </c>
       <c r="D2" t="n">
-        <v>12143</v>
+        <v>17620</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3235</v>
+        <v>347</v>
       </c>
       <c r="C3" t="n">
-        <v>3676</v>
+        <v>3388</v>
       </c>
       <c r="D3" t="n">
-        <v>10188</v>
+        <v>9930</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3633</v>
+        <v>508</v>
       </c>
       <c r="C4" t="n">
-        <v>6542</v>
+        <v>3564</v>
       </c>
       <c r="D4" t="n">
-        <v>9398</v>
+        <v>10296</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3114</v>
+        <v>691</v>
       </c>
       <c r="C5" t="n">
-        <v>8858</v>
+        <v>4540</v>
       </c>
       <c r="D5" t="n">
-        <v>5235</v>
+        <v>7138</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1817</v>
+        <v>560</v>
       </c>
       <c r="C6" t="n">
-        <v>8688</v>
+        <v>5174</v>
       </c>
       <c r="D6" t="n">
-        <v>2066</v>
+        <v>3204</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>554</v>
+        <v>252</v>
       </c>
       <c r="C7" t="n">
-        <v>6358</v>
+        <v>4679</v>
       </c>
       <c r="D7" t="n">
-        <v>803</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>100</v>
+        <v>66</v>
       </c>
       <c r="C8" t="n">
-        <v>3522</v>
+        <v>2706</v>
       </c>
       <c r="D8" t="n">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="C9" t="n">
-        <v>1301</v>
+        <v>998</v>
       </c>
       <c r="D9" t="n">
-        <v>292</v>
+        <v>231</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C10" t="n">
-        <v>349</v>
+        <v>317</v>
       </c>
       <c r="D10" t="n">
-        <v>184</v>
+        <v>151</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>147</v>
+        <v>134</v>
       </c>
       <c r="D11" t="n">
-        <v>135</v>
+        <v>106</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="D12" t="n">
-        <v>93</v>
+        <v>69</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>36</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>36</v>
+        <v>54</v>
       </c>
       <c r="D14" t="n">
-        <v>35</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>58</v>
+        <v>24</v>
       </c>
       <c r="D15" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>64</v>
+        <v>3</v>
       </c>
       <c r="D16" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7405</v>
+        <v>4132</v>
       </c>
       <c r="C2" t="n">
-        <v>13062</v>
+        <v>6364</v>
       </c>
       <c r="D2" t="n">
-        <v>14382</v>
+        <v>10124</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>843</v>
+        <v>855</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>175</v>
+        <v>205</v>
       </c>
       <c r="C4" t="n">
-        <v>313</v>
+        <v>344</v>
       </c>
       <c r="D4" t="n">
-        <v>1805</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>249</v>
+        <v>314</v>
       </c>
       <c r="C5" t="n">
-        <v>515</v>
+        <v>586</v>
       </c>
       <c r="D5" t="n">
-        <v>1038</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>182</v>
+        <v>255</v>
       </c>
       <c r="C6" t="n">
-        <v>395</v>
+        <v>488</v>
       </c>
       <c r="D6" t="n">
-        <v>777</v>
+        <v>898</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>129</v>
+        <v>202</v>
       </c>
       <c r="C7" t="n">
-        <v>293</v>
+        <v>388</v>
       </c>
       <c r="D7" t="n">
-        <v>496</v>
+        <v>596</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>99</v>
+        <v>171</v>
       </c>
       <c r="C8" t="n">
-        <v>222</v>
+        <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>420</v>
+        <v>531</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>75</v>
+        <v>136</v>
       </c>
       <c r="C9" t="n">
-        <v>187</v>
+        <v>277</v>
       </c>
       <c r="D9" t="n">
-        <v>349</v>
+        <v>445</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>53</v>
+        <v>105</v>
       </c>
       <c r="C10" t="n">
-        <v>173</v>
+        <v>265</v>
       </c>
       <c r="D10" t="n">
-        <v>362</v>
+        <v>485</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>34</v>
+        <v>71</v>
       </c>
       <c r="C11" t="n">
-        <v>137</v>
+        <v>215</v>
       </c>
       <c r="D11" t="n">
-        <v>245</v>
+        <v>327</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="C12" t="n">
-        <v>104</v>
+        <v>169</v>
       </c>
       <c r="D12" t="n">
-        <v>196</v>
+        <v>274</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="C13" t="n">
-        <v>84</v>
+        <v>142</v>
       </c>
       <c r="D13" t="n">
-        <v>168</v>
+        <v>234</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C14" t="n">
-        <v>75</v>
+        <v>128</v>
       </c>
       <c r="D14" t="n">
-        <v>145</v>
+        <v>207</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C15" t="n">
-        <v>72</v>
+        <v>127</v>
       </c>
       <c r="D15" t="n">
-        <v>117</v>
+        <v>171</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>124</v>
       </c>
       <c r="D16" t="n">
-        <v>97</v>
+        <v>140</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="C17" t="n">
-        <v>66</v>
+        <v>119</v>
       </c>
       <c r="D17" t="n">
-        <v>76</v>
+        <v>114</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C18" t="n">
-        <v>63</v>
+        <v>116</v>
       </c>
       <c r="D18" t="n">
-        <v>57</v>
+        <v>85</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C19" t="n">
-        <v>60</v>
+        <v>111</v>
       </c>
       <c r="D19" t="n">
-        <v>38</v>
+        <v>58</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>109</v>
       </c>
       <c r="D20" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="21">
@@ -4156,10 +4156,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C21" t="n">
-        <v>72</v>
+        <v>131</v>
       </c>
       <c r="D21" t="n">
         <v>1</v>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3010</v>
+        <v>973</v>
       </c>
       <c r="C2" t="n">
-        <v>5215</v>
+        <v>9511</v>
       </c>
       <c r="D2" t="n">
-        <v>9034</v>
+        <v>21172</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4254</v>
+        <v>359</v>
       </c>
       <c r="C3" t="n">
-        <v>5141</v>
+        <v>5608</v>
       </c>
       <c r="D3" t="n">
-        <v>11182</v>
+        <v>10308</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>4705</v>
+        <v>385</v>
       </c>
       <c r="C4" t="n">
-        <v>9476</v>
+        <v>3407</v>
       </c>
       <c r="D4" t="n">
-        <v>9556</v>
+        <v>9923</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1707</v>
+        <v>564</v>
       </c>
       <c r="C5" t="n">
-        <v>12594</v>
+        <v>3961</v>
       </c>
       <c r="D5" t="n">
-        <v>4801</v>
+        <v>7406</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>511</v>
+        <v>573</v>
       </c>
       <c r="C6" t="n">
-        <v>7678</v>
+        <v>4844</v>
       </c>
       <c r="D6" t="n">
-        <v>1684</v>
+        <v>3696</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>92</v>
+        <v>337</v>
       </c>
       <c r="C7" t="n">
-        <v>3451</v>
+        <v>4890</v>
       </c>
       <c r="D7" t="n">
-        <v>512</v>
+        <v>1379</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>18</v>
+        <v>122</v>
       </c>
       <c r="C8" t="n">
-        <v>1274</v>
+        <v>3490</v>
       </c>
       <c r="D8" t="n">
-        <v>286</v>
+        <v>508</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="C9" t="n">
-        <v>342</v>
+        <v>1683</v>
       </c>
       <c r="D9" t="n">
-        <v>180</v>
+        <v>255</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C10" t="n">
-        <v>144</v>
+        <v>577</v>
       </c>
       <c r="D10" t="n">
-        <v>132</v>
+        <v>158</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>82</v>
+        <v>198</v>
       </c>
       <c r="D11" t="n">
-        <v>91</v>
+        <v>110</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>47</v>
+        <v>95</v>
       </c>
       <c r="D12" t="n">
-        <v>59</v>
+        <v>72</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="D13" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
     </row>
     <row r="14">
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D14" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>62</v>
+        <v>32</v>
       </c>
       <c r="D15" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7452</v>
+        <v>5174</v>
       </c>
       <c r="C2" t="n">
-        <v>9111</v>
+        <v>11016</v>
       </c>
       <c r="D2" t="n">
-        <v>14300</v>
+        <v>25501</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3145</v>
+        <v>1366</v>
       </c>
       <c r="C3" t="n">
-        <v>6583</v>
+        <v>2513</v>
       </c>
       <c r="D3" t="n">
-        <v>3055</v>
+        <v>1999</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="C4" t="n">
-        <v>117</v>
+        <v>134</v>
       </c>
       <c r="D4" t="n">
-        <v>1538</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>193</v>
+        <v>148</v>
       </c>
       <c r="C5" t="n">
-        <v>385</v>
+        <v>334</v>
       </c>
       <c r="D5" t="n">
-        <v>1161</v>
+        <v>986</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>200</v>
+        <v>143</v>
       </c>
       <c r="C6" t="n">
-        <v>458</v>
+        <v>360</v>
       </c>
       <c r="D6" t="n">
-        <v>816</v>
+        <v>712</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>102</v>
       </c>
       <c r="C7" t="n">
-        <v>346</v>
+        <v>277</v>
       </c>
       <c r="D7" t="n">
-        <v>538</v>
+        <v>466</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>106</v>
+        <v>78</v>
       </c>
       <c r="C8" t="n">
-        <v>260</v>
+        <v>206</v>
       </c>
       <c r="D8" t="n">
-        <v>429</v>
+        <v>384</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>79</v>
+        <v>60</v>
       </c>
       <c r="C9" t="n">
-        <v>205</v>
+        <v>169</v>
       </c>
       <c r="D9" t="n">
-        <v>357</v>
+        <v>313</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="C10" t="n">
-        <v>180</v>
+        <v>151</v>
       </c>
       <c r="D10" t="n">
-        <v>352</v>
+        <v>324</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="C11" t="n">
-        <v>154</v>
+        <v>129</v>
       </c>
       <c r="D11" t="n">
-        <v>261</v>
+        <v>231</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C12" t="n">
-        <v>119</v>
+        <v>100</v>
       </c>
       <c r="D12" t="n">
-        <v>199</v>
+        <v>182</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="D13" t="n">
-        <v>170</v>
+        <v>154</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>133</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="D15" t="n">
-        <v>118</v>
+        <v>111</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>89</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C17" t="n">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="D18" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20">
@@ -4767,10 +4767,10 @@
         <v>10</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C21" t="n">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="D21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6362</v>
+        <v>2687</v>
       </c>
       <c r="C2" t="n">
-        <v>8252</v>
+        <v>8066</v>
       </c>
       <c r="D2" t="n">
-        <v>19686</v>
+        <v>29383</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4353</v>
+        <v>2770</v>
       </c>
       <c r="C3" t="n">
-        <v>6910</v>
+        <v>6572</v>
       </c>
       <c r="D3" t="n">
-        <v>4719</v>
+        <v>5985</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1400</v>
+        <v>657</v>
       </c>
       <c r="C4" t="n">
-        <v>3901</v>
+        <v>1615</v>
       </c>
       <c r="D4" t="n">
-        <v>1797</v>
+        <v>1518</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="C5" t="n">
-        <v>225</v>
+        <v>206</v>
       </c>
       <c r="D5" t="n">
-        <v>1198</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>185</v>
+        <v>135</v>
       </c>
       <c r="C6" t="n">
-        <v>412</v>
+        <v>343</v>
       </c>
       <c r="D6" t="n">
-        <v>859</v>
+        <v>747</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>160</v>
+        <v>114</v>
       </c>
       <c r="C7" t="n">
-        <v>402</v>
+        <v>324</v>
       </c>
       <c r="D7" t="n">
-        <v>584</v>
+        <v>509</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>114</v>
+        <v>83</v>
       </c>
       <c r="C8" t="n">
-        <v>305</v>
+        <v>244</v>
       </c>
       <c r="D8" t="n">
-        <v>443</v>
+        <v>395</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85</v>
+        <v>64</v>
       </c>
       <c r="C9" t="n">
-        <v>232</v>
+        <v>188</v>
       </c>
       <c r="D9" t="n">
-        <v>361</v>
+        <v>319</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>62</v>
+        <v>47</v>
       </c>
       <c r="C10" t="n">
-        <v>192</v>
+        <v>160</v>
       </c>
       <c r="D10" t="n">
-        <v>349</v>
+        <v>318</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="C11" t="n">
-        <v>166</v>
+        <v>139</v>
       </c>
       <c r="D11" t="n">
-        <v>270</v>
+        <v>244</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C12" t="n">
-        <v>133</v>
+        <v>113</v>
       </c>
       <c r="D12" t="n">
-        <v>206</v>
+        <v>187</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
-        <v>172</v>
+        <v>155</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>134</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C15" t="n">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>90</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="20">
@@ -5078,10 +5078,10 @@
         <v>9</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C21" t="n">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="D21" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6133</v>
+        <v>2979</v>
       </c>
       <c r="C2" t="n">
-        <v>6068</v>
+        <v>4501</v>
       </c>
       <c r="D2" t="n">
-        <v>16651</v>
+        <v>24594</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4371</v>
+        <v>2250</v>
       </c>
       <c r="C3" t="n">
-        <v>6615</v>
+        <v>6398</v>
       </c>
       <c r="D3" t="n">
-        <v>6773</v>
+        <v>9475</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2412</v>
+        <v>1507</v>
       </c>
       <c r="C4" t="n">
-        <v>5495</v>
+        <v>4531</v>
       </c>
       <c r="D4" t="n">
-        <v>2303</v>
+        <v>2372</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>624</v>
+        <v>327</v>
       </c>
       <c r="C5" t="n">
-        <v>2196</v>
+        <v>1013</v>
       </c>
       <c r="D5" t="n">
-        <v>1270</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>147</v>
+        <v>111</v>
       </c>
       <c r="C6" t="n">
-        <v>306</v>
+        <v>262</v>
       </c>
       <c r="D6" t="n">
-        <v>897</v>
+        <v>794</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>160</v>
+        <v>115</v>
       </c>
       <c r="C7" t="n">
-        <v>407</v>
+        <v>334</v>
       </c>
       <c r="D7" t="n">
-        <v>626</v>
+        <v>548</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>124</v>
+        <v>91</v>
       </c>
       <c r="C8" t="n">
-        <v>353</v>
+        <v>286</v>
       </c>
       <c r="D8" t="n">
-        <v>457</v>
+        <v>407</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>91</v>
+        <v>67</v>
       </c>
       <c r="C9" t="n">
-        <v>264</v>
+        <v>216</v>
       </c>
       <c r="D9" t="n">
-        <v>370</v>
+        <v>329</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="C10" t="n">
-        <v>210</v>
+        <v>173</v>
       </c>
       <c r="D10" t="n">
-        <v>347</v>
+        <v>314</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="C11" t="n">
-        <v>177</v>
+        <v>148</v>
       </c>
       <c r="D11" t="n">
-        <v>276</v>
+        <v>253</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C12" t="n">
-        <v>147</v>
+        <v>124</v>
       </c>
       <c r="D12" t="n">
-        <v>213</v>
+        <v>191</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C13" t="n">
-        <v>114</v>
+        <v>98</v>
       </c>
       <c r="D13" t="n">
-        <v>173</v>
+        <v>158</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C15" t="n">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="D15" t="n">
-        <v>122</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C17" t="n">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C21" t="n">
-        <v>121</v>
+        <v>106</v>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7601</v>
+        <v>3017</v>
       </c>
       <c r="C2" t="n">
-        <v>10718</v>
+        <v>4219</v>
       </c>
       <c r="D2" t="n">
-        <v>22091</v>
+        <v>32351</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4267</v>
+        <v>2145</v>
       </c>
       <c r="C3" t="n">
-        <v>5527</v>
+        <v>4642</v>
       </c>
       <c r="D3" t="n">
-        <v>7797</v>
+        <v>11211</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2863</v>
+        <v>1606</v>
       </c>
       <c r="C4" t="n">
-        <v>5972</v>
+        <v>5494</v>
       </c>
       <c r="D4" t="n">
-        <v>3048</v>
+        <v>3663</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1232</v>
+        <v>779</v>
       </c>
       <c r="C5" t="n">
-        <v>3828</v>
+        <v>2916</v>
       </c>
       <c r="D5" t="n">
-        <v>1409</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>328</v>
+        <v>196</v>
       </c>
       <c r="C6" t="n">
-        <v>1225</v>
+        <v>655</v>
       </c>
       <c r="D6" t="n">
-        <v>936</v>
+        <v>837</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>144</v>
+        <v>105</v>
       </c>
       <c r="C7" t="n">
-        <v>357</v>
+        <v>296</v>
       </c>
       <c r="D7" t="n">
-        <v>664</v>
+        <v>585</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>130</v>
+        <v>95</v>
       </c>
       <c r="C8" t="n">
-        <v>374</v>
+        <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>474</v>
+        <v>422</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>96</v>
+        <v>72</v>
       </c>
       <c r="C9" t="n">
-        <v>304</v>
+        <v>250</v>
       </c>
       <c r="D9" t="n">
-        <v>379</v>
+        <v>338</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="C10" t="n">
-        <v>233</v>
+        <v>193</v>
       </c>
       <c r="D10" t="n">
-        <v>343</v>
+        <v>313</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="C11" t="n">
-        <v>189</v>
+        <v>159</v>
       </c>
       <c r="D11" t="n">
-        <v>283</v>
+        <v>256</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C12" t="n">
-        <v>159</v>
+        <v>134</v>
       </c>
       <c r="D12" t="n">
-        <v>219</v>
+        <v>198</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C13" t="n">
-        <v>126</v>
+        <v>108</v>
       </c>
       <c r="D13" t="n">
-        <v>174</v>
+        <v>160</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>98</v>
+        <v>86</v>
       </c>
       <c r="D14" t="n">
-        <v>149</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="D15" t="n">
-        <v>122</v>
+        <v>113</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C16" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="D16" t="n">
-        <v>100</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C17" t="n">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="D20" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C21" t="n">
-        <v>136</v>
+        <v>120</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8681</v>
+        <v>3288</v>
       </c>
       <c r="C2" t="n">
-        <v>8374</v>
+        <v>5065</v>
       </c>
       <c r="D2" t="n">
-        <v>23778</v>
+        <v>37798</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4240</v>
+        <v>2097</v>
       </c>
       <c r="C3" t="n">
-        <v>6625</v>
+        <v>3850</v>
       </c>
       <c r="D3" t="n">
-        <v>8757</v>
+        <v>13635</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2200</v>
+        <v>1593</v>
       </c>
       <c r="C4" t="n">
-        <v>4641</v>
+        <v>4921</v>
       </c>
       <c r="D4" t="n">
-        <v>3262</v>
+        <v>4928</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1046</v>
+        <v>1026</v>
       </c>
       <c r="C5" t="n">
-        <v>3586</v>
+        <v>4191</v>
       </c>
       <c r="D5" t="n">
-        <v>1335</v>
+        <v>1643</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>360</v>
+        <v>414</v>
       </c>
       <c r="C6" t="n">
-        <v>1665</v>
+        <v>1776</v>
       </c>
       <c r="D6" t="n">
-        <v>763</v>
+        <v>902</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>101</v>
+        <v>134</v>
       </c>
       <c r="C7" t="n">
-        <v>493</v>
+        <v>471</v>
       </c>
       <c r="D7" t="n">
-        <v>519</v>
+        <v>621</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>58</v>
+        <v>92</v>
       </c>
       <c r="C8" t="n">
-        <v>223</v>
+        <v>298</v>
       </c>
       <c r="D8" t="n">
-        <v>353</v>
+        <v>439</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>44</v>
+        <v>76</v>
       </c>
       <c r="C9" t="n">
-        <v>194</v>
+        <v>276</v>
       </c>
       <c r="D9" t="n">
-        <v>272</v>
+        <v>347</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="C10" t="n">
-        <v>149</v>
+        <v>218</v>
       </c>
       <c r="D10" t="n">
-        <v>233</v>
+        <v>310</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="C11" t="n">
-        <v>113</v>
+        <v>173</v>
       </c>
       <c r="D11" t="n">
-        <v>194</v>
+        <v>261</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>92</v>
+        <v>143</v>
       </c>
       <c r="D12" t="n">
-        <v>147</v>
+        <v>203</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="C13" t="n">
-        <v>72</v>
+        <v>116</v>
       </c>
       <c r="D13" t="n">
-        <v>116</v>
+        <v>161</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>56</v>
+        <v>94</v>
       </c>
       <c r="D14" t="n">
-        <v>96</v>
+        <v>136</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>44</v>
+        <v>76</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C16" t="n">
-        <v>38</v>
+        <v>67</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C17" t="n">
-        <v>34</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>49</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C18" t="n">
-        <v>32</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>57</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>53</v>
       </c>
       <c r="D20" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21">
@@ -6022,10 +6022,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>75</v>
+        <v>132</v>
       </c>
       <c r="D21" t="n">
         <v>5</v>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7937</v>
+        <v>2256</v>
       </c>
       <c r="C2" t="n">
-        <v>5645</v>
+        <v>7049</v>
       </c>
       <c r="D2" t="n">
-        <v>20544</v>
+        <v>33136</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5311</v>
+        <v>2175</v>
       </c>
       <c r="C3" t="n">
-        <v>6566</v>
+        <v>3881</v>
       </c>
       <c r="D3" t="n">
-        <v>10636</v>
+        <v>16176</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2779</v>
+        <v>1555</v>
       </c>
       <c r="C4" t="n">
-        <v>5661</v>
+        <v>4284</v>
       </c>
       <c r="D4" t="n">
-        <v>4270</v>
+        <v>6282</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1439</v>
+        <v>1138</v>
       </c>
       <c r="C5" t="n">
-        <v>4119</v>
+        <v>4413</v>
       </c>
       <c r="D5" t="n">
-        <v>1651</v>
+        <v>2113</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>643</v>
+        <v>612</v>
       </c>
       <c r="C6" t="n">
-        <v>2714</v>
+        <v>2893</v>
       </c>
       <c r="D6" t="n">
-        <v>861</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>204</v>
+        <v>225</v>
       </c>
       <c r="C7" t="n">
-        <v>1135</v>
+        <v>1071</v>
       </c>
       <c r="D7" t="n">
-        <v>559</v>
+        <v>658</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>72</v>
+        <v>101</v>
       </c>
       <c r="C8" t="n">
-        <v>365</v>
+        <v>371</v>
       </c>
       <c r="D8" t="n">
-        <v>375</v>
+        <v>456</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>46</v>
+        <v>76</v>
       </c>
       <c r="C9" t="n">
-        <v>208</v>
+        <v>285</v>
       </c>
       <c r="D9" t="n">
-        <v>283</v>
+        <v>356</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>33</v>
+        <v>58</v>
       </c>
       <c r="C10" t="n">
-        <v>169</v>
+        <v>241</v>
       </c>
       <c r="D10" t="n">
-        <v>237</v>
+        <v>308</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="C11" t="n">
-        <v>130</v>
+        <v>188</v>
       </c>
       <c r="D11" t="n">
-        <v>196</v>
+        <v>265</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="C12" t="n">
-        <v>101</v>
+        <v>154</v>
       </c>
       <c r="D12" t="n">
-        <v>152</v>
+        <v>208</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="C13" t="n">
-        <v>80</v>
+        <v>125</v>
       </c>
       <c r="D13" t="n">
-        <v>119</v>
+        <v>162</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>62</v>
+        <v>100</v>
       </c>
       <c r="D14" t="n">
-        <v>96</v>
+        <v>137</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>48</v>
+        <v>81</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C16" t="n">
-        <v>39</v>
+        <v>69</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>93</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>63</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>32</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>57</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>40</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>53</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21">
@@ -6333,10 +6333,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>83</v>
+        <v>143</v>
       </c>
       <c r="D21" t="n">
         <v>6</v>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7821</v>
+        <v>2156</v>
       </c>
       <c r="C2" t="n">
-        <v>7194</v>
+        <v>4398</v>
       </c>
       <c r="D2" t="n">
-        <v>18080</v>
+        <v>26024</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5382</v>
+        <v>2825</v>
       </c>
       <c r="C3" t="n">
-        <v>5284</v>
+        <v>6405</v>
       </c>
       <c r="D3" t="n">
-        <v>11393</v>
+        <v>17762</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3405</v>
+        <v>1051</v>
       </c>
       <c r="C4" t="n">
-        <v>6038</v>
+        <v>6909</v>
       </c>
       <c r="D4" t="n">
-        <v>5260</v>
+        <v>5681</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1833</v>
+        <v>565</v>
       </c>
       <c r="C5" t="n">
-        <v>4847</v>
+        <v>2835</v>
       </c>
       <c r="D5" t="n">
-        <v>2078</v>
+        <v>1618</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>923</v>
+        <v>207</v>
       </c>
       <c r="C6" t="n">
-        <v>3372</v>
+        <v>1049</v>
       </c>
       <c r="D6" t="n">
-        <v>985</v>
+        <v>644</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>366</v>
+        <v>93</v>
       </c>
       <c r="C7" t="n">
-        <v>1939</v>
+        <v>363</v>
       </c>
       <c r="D7" t="n">
-        <v>598</v>
+        <v>446</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>117</v>
+        <v>70</v>
       </c>
       <c r="C8" t="n">
-        <v>742</v>
+        <v>279</v>
       </c>
       <c r="D8" t="n">
-        <v>401</v>
+        <v>348</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C9" t="n">
-        <v>281</v>
+        <v>236</v>
       </c>
       <c r="D9" t="n">
-        <v>291</v>
+        <v>301</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C10" t="n">
         <v>184</v>
       </c>
       <c r="D10" t="n">
-        <v>241</v>
+        <v>259</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C11" t="n">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D11" t="n">
-        <v>198</v>
+        <v>203</v>
       </c>
     </row>
     <row r="12">
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="D12" t="n">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="D13" t="n">
-        <v>122</v>
+        <v>134</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C14" t="n">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="D14" t="n">
-        <v>97</v>
+        <v>111</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C15" t="n">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="D15" t="n">
-        <v>81</v>
+        <v>91</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C16" t="n">
-        <v>41</v>
+        <v>61</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>74</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>36</v>
+        <v>57</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
     </row>
     <row r="18">
@@ -6602,13 +6602,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C18" t="n">
-        <v>32</v>
+        <v>54</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>143</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
